--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Company\GIT\jy_aps\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6674513-7BAB-4938-A28C-E16C9648AE30}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21600" windowHeight="9555" tabRatio="844"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="1" r:id="rId1"/>
@@ -21,6 +20,19 @@
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -273,612 +285,40 @@
     <t>remark</t>
   </si>
   <si>
-    <t xml:space="preserve"> 版本号phiên bản：{productionVersion}</t>
-  </si>
-  <si>
-    <t>班产合计
-Tổng kế hoạch：</t>
-  </si>
-  <si>
-    <t>合计
-Tổng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">总计
-</t>
-  </si>
-  <si>
-    <t>*机台</t>
-  </si>
-  <si>
-    <t>硫化物料号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">物料描述
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*胎胚编码
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">胎胚描述
-</t>
-  </si>
-  <si>
-    <t>结构</t>
-  </si>
-  <si>
-    <t>合计余量</t>
-  </si>
-  <si>
-    <t xml:space="preserve">胎胚库存
-</t>
-  </si>
-  <si>
-    <t>胶囊次数L/R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">硫化班产
-</t>
-  </si>
-  <si>
-    <t>早班 Ca sáng {shiftDate1}</t>
-  </si>
-  <si>
-    <t>中班 Ca chiều {shiftDate2}</t>
-  </si>
-  <si>
-    <t>夜班 Ca đêm {shiftDate3}</t>
-  </si>
-  <si>
-    <t>早班 Ca sáng {shiftDate4}</t>
-  </si>
-  <si>
-    <t>中班 Ca chiều {shiftDate5}</t>
-  </si>
-  <si>
-    <t>夜班 Ca đêm {shiftDate6}</t>
-  </si>
-  <si>
-    <t>早班 Ca sáng {shiftDate7}</t>
-  </si>
-  <si>
-    <t>中班 Ca chiều {shiftDate8}</t>
-  </si>
-  <si>
-    <t>对应成型机台号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月计划订单总量
-</t>
-  </si>
-  <si>
-    <t>本月硫化产量（今天夜班）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">备注
-</t>
-  </si>
-  <si>
-    <t>计划
-Kế hoạch</t>
-  </si>
-  <si>
-    <t>实际
-Thực tế</t>
-  </si>
-  <si>
-    <t>Tổng</t>
-  </si>
-  <si>
-    <t>Máy</t>
-  </si>
-  <si>
-    <t>Mã NC</t>
-  </si>
-  <si>
-    <t>Quy cách lưu hóa</t>
-  </si>
-  <si>
-    <t>Mã vật liệu</t>
-  </si>
-  <si>
-    <t>Phôi thành hình</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUY CÁCH </t>
-  </si>
-  <si>
-    <t>Số còn thiếu</t>
-  </si>
-  <si>
-    <t>Phôi tồn</t>
-  </si>
-  <si>
-    <t>Số lần sử dụng phao L/R</t>
-  </si>
-  <si>
-    <t>Lưu hóa trong ca</t>
-  </si>
-  <si>
-    <t>*顺序
-Stt</t>
-  </si>
-  <si>
-    <t>*计划
-Kế hoạch</t>
-  </si>
-  <si>
-    <t>左右模
-Khuôn trái phải</t>
-  </si>
-  <si>
-    <t>类型
-Loại hình</t>
-  </si>
-  <si>
-    <t>*示方类型
-Phương thức</t>
-  </si>
-  <si>
-    <t>*备注
-Chú ý</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*DOT DOT
-</t>
-  </si>
-  <si>
-    <t>Tương ứng máy TH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đơn hàng </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sản lượng lưu hóa đạt </t>
-  </si>
-  <si>
-    <t>Ghi chú</t>
-  </si>
-  <si>
-    <t>{.sameMaterialPlanQtyTotal}</t>
-  </si>
-  <si>
-    <t>{.nightPlanQtyTotal}</t>
-  </si>
-  <si>
-    <t>{.nightFinishQtyTotal}</t>
-  </si>
-  <si>
-    <t>{.totalPlanQtyFormula}</t>
-  </si>
-  <si>
-    <t>{.lhMachineCode}</t>
-  </si>
-  <si>
-    <t>{.materialCode}</t>
-  </si>
-  <si>
-    <t>{.materialDesc}</t>
-  </si>
-  <si>
-    <t>{.embryoCode}</t>
-  </si>
-  <si>
-    <t>{.mainMaterialDesc}</t>
-  </si>
-  <si>
-    <t>{.structureName}</t>
-  </si>
-  <si>
-    <t>{.dailyPlanQty}</t>
-  </si>
-  <si>
-    <t>{.embryoStock}</t>
-  </si>
-  <si>
-    <t>{.replaceCapsuleCountLeftRight}</t>
-  </si>
-  <si>
-    <t>{.singleMouldShiftQty}</t>
-  </si>
-  <si>
-    <t>{.class1Order}</t>
-  </si>
-  <si>
-    <t>{.class1PlanQty}</t>
-  </si>
-  <si>
-    <t>{.class1FinishQty}</t>
-  </si>
-  <si>
-    <t>{.class1LeftRightMould}</t>
-  </si>
-  <si>
-    <t>{.class1IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class1LhType}</t>
-  </si>
-  <si>
-    <t>{.class1Analysis}</t>
-  </si>
-  <si>
-    <t>{.class1Dot}</t>
-  </si>
-  <si>
-    <t>{.class2Order}</t>
-  </si>
-  <si>
-    <t>{.class2PlanQty}</t>
-  </si>
-  <si>
-    <t>{.class2FinishQty}</t>
-  </si>
-  <si>
-    <t>{.class2LeftRightMould}</t>
-  </si>
-  <si>
-    <t>{.class2IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class2LhType}</t>
-  </si>
-  <si>
-    <t>{.class2Analysis}</t>
-  </si>
-  <si>
-    <t>{.class2Dot}</t>
-  </si>
-  <si>
-    <t>{.class3Order}</t>
-  </si>
-  <si>
-    <t>{.class3PlanQty}</t>
-  </si>
-  <si>
-    <t>{.class3FinishQty}</t>
-  </si>
-  <si>
-    <t>{.class3LeftRightMould}</t>
-  </si>
-  <si>
-    <t>{.class3IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class3LhType}</t>
-  </si>
-  <si>
-    <t>{.class3Analysis}</t>
-  </si>
-  <si>
-    <t>{.class3Dot}</t>
-  </si>
-  <si>
-    <t>{.class4Order}</t>
-  </si>
-  <si>
-    <t>{.class4PlanQty}</t>
-  </si>
-  <si>
-    <t>{.class4FinishQty}</t>
-  </si>
-  <si>
-    <t>{.class4LeftRightMould}</t>
-  </si>
-  <si>
-    <t>{.class4IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class4LhType}</t>
-  </si>
-  <si>
-    <t>{.class4Analysis}</t>
-  </si>
-  <si>
-    <t>{.class4Dot}</t>
-  </si>
-  <si>
-    <t>{.class5Order}</t>
-  </si>
-  <si>
-    <t>{.class5PlanQty}</t>
-  </si>
-  <si>
-    <t>{.class5FinishQty}</t>
-  </si>
-  <si>
-    <t>{.class5LeftRightMould}</t>
-  </si>
-  <si>
-    <t>{.class5IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class5LhType}</t>
-  </si>
-  <si>
-    <t>{.class5Analysis}</t>
-  </si>
-  <si>
-    <t>{.class5Dot}</t>
-  </si>
-  <si>
-    <t>{.class6Order}</t>
-  </si>
-  <si>
-    <t>{.class6PlanQty}</t>
-  </si>
-  <si>
-    <t>{.class6FinishQty}</t>
-  </si>
-  <si>
-    <t>{.class6LeftRightMould}</t>
-  </si>
-  <si>
-    <t>{.class6IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class6LhType}</t>
-  </si>
-  <si>
-    <t>{.class6Analysis}</t>
-  </si>
-  <si>
-    <t>{.class6Dot}</t>
-  </si>
-  <si>
-    <t>{.class7Order}</t>
-  </si>
-  <si>
-    <t>{.class7PlanQty}</t>
-  </si>
-  <si>
-    <t>{.class7FinishQty}</t>
-  </si>
-  <si>
-    <t>{.class7LeftRightMould}</t>
-  </si>
-  <si>
-    <t>{.class7IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class7LhType}</t>
-  </si>
-  <si>
-    <t>{.class7Analysis}</t>
-  </si>
-  <si>
-    <t>{.class7Dot}</t>
-  </si>
-  <si>
-    <t>{.class8Order}</t>
-  </si>
-  <si>
-    <t>{.class8PlanQty}</t>
-  </si>
-  <si>
-    <t>{.class8FinishQty}</t>
-  </si>
-  <si>
-    <t>{.class8LeftRightMould}</t>
-  </si>
-  <si>
-    <t>{.class8IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class8LhType}</t>
-  </si>
-  <si>
-    <t>{.class8Analysis}</t>
-  </si>
-  <si>
-    <t>{.class8Dot}</t>
-  </si>
-  <si>
-    <t>{.cxMachineCode}</t>
-  </si>
-  <si>
-    <t>{.totalDailyPlanQty}</t>
-  </si>
-  <si>
-    <t>{.todayNightFinishQty}</t>
-  </si>
-  <si>
-    <t>{.remark}</t>
-  </si>
-  <si>
-    <t>{seq}</t>
-  </si>
-  <si>
-    <t>{planDate}</t>
-  </si>
-  <si>
-    <t>{classIndex}</t>
-  </si>
-  <si>
-    <t>{lhMachineCode}</t>
-  </si>
-  <si>
-    <t>{leftRightMould}</t>
-  </si>
-  <si>
-    <t>{beforeMaterialCode}</t>
-  </si>
-  <si>
-    <t>{beforeMaterialDesc}</t>
-  </si>
-  <si>
-    <t>{afterMaterialCode}</t>
-  </si>
-  <si>
-    <t>{afterMaterialDesc}</t>
-  </si>
-  <si>
-    <t>{afterMaterialType}</t>
-  </si>
-  <si>
-    <t>{changeType}</t>
-  </si>
-  <si>
-    <t>{isDryIceClean}</t>
-  </si>
-  <si>
-    <t>{isSandblastingClean}</t>
-  </si>
-  <si>
-    <t>{isReplaceBlock}</t>
-  </si>
-  <si>
-    <t>{mouldCode}</t>
-  </si>
-  <si>
-    <t>{remark}</t>
-  </si>
-  <si>
-    <t>{title}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">序号
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">计划日期
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">班次
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">机台
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">左右模
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当前物料
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">计划物料 
-</t>
-  </si>
-  <si>
-    <t>示方类型</t>
-  </si>
-  <si>
-    <t>按时间下机</t>
-  </si>
-  <si>
-    <t>干冰清洗</t>
-  </si>
-  <si>
-    <t>喷砂清洗</t>
-  </si>
-  <si>
-    <t>只换活字块</t>
-  </si>
-  <si>
-    <t>模具号</t>
-  </si>
-  <si>
-    <t>TT</t>
-  </si>
-  <si>
-    <t>Ngày tháng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca thay </t>
-  </si>
-  <si>
-    <t>Trái phải của khuôn</t>
-  </si>
-  <si>
-    <t>Mã liệu kế hoạch  đang lưu hóa (trước khi thay)</t>
-  </si>
-  <si>
-    <t>Mô tả vật liệu (trước khi thay)</t>
-  </si>
-  <si>
-    <t>Mã liệu kế hoạch  (sau khi thay)</t>
-  </si>
-  <si>
-    <t>Mô tả vật liệu (sau khi thay)</t>
-  </si>
-  <si>
-    <t>Loại phương thức</t>
-  </si>
-  <si>
-    <t>Xuống máy theo thời gian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vệ sinh đá </t>
-  </si>
-  <si>
-    <t>Vệ sinh cát （VSC）</t>
-  </si>
-  <si>
-    <t>Chỉ thay lắc</t>
-  </si>
-  <si>
-    <t>Mã số khuôn （MSK）</t>
-  </si>
-  <si>
-    <t>{.seq}</t>
-  </si>
-  <si>
-    <t>{.planDate}</t>
-  </si>
-  <si>
-    <t>{.classIndex}</t>
-  </si>
-  <si>
-    <t>{.leftRightMould}</t>
-  </si>
-  <si>
-    <t>{.beforeMaterialCode}</t>
-  </si>
-  <si>
-    <t>{.beforeMaterialDesc}</t>
-  </si>
-  <si>
-    <t>{.afterMaterialCode}</t>
-  </si>
-  <si>
-    <t>{.afterMaterialDesc}</t>
-  </si>
-  <si>
-    <t>{.afterMaterialType}</t>
-  </si>
-  <si>
-    <t>{.endType}</t>
-  </si>
-  <si>
-    <t>{.isDryIceClean}</t>
-  </si>
-  <si>
-    <t>{.isSandblastingClean}</t>
-  </si>
-  <si>
-    <t>{.isReplaceBlock}</t>
-  </si>
-  <si>
-    <t>{.mouldCode}</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">{yearmonthday}全钢硫化工程生产计划单
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{yearmonthday}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全钢硫化工程生产计划单</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -886,8 +326,7 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>n k</t>
@@ -896,8 +335,8 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -905,8 +344,7 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -915,8 +353,8 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -924,8 +362,7 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>ch s</t>
@@ -934,8 +371,8 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -943,8 +380,7 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>n xu</t>
@@ -953,8 +389,8 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>ấ</t>
     </r>
@@ -962,8 +398,7 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>t c</t>
@@ -972,8 +407,8 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -981,8 +416,7 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a công </t>
@@ -991,8 +425,8 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -1000,8 +434,7 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>o</t>
@@ -1010,8 +443,8 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -1019,8 +452,7 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>n l</t>
@@ -1029,8 +461,8 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Cambria"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1038,29 +470,696 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa toàn thép</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>版本号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>phiên bản</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{productionVersion}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>班产合计</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+Tổng kế hoạch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+  </si>
+  <si>
+    <t>合计
+Tổng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">总计
+</t>
+  </si>
+  <si>
+    <t>*机台</t>
+  </si>
+  <si>
+    <t>硫化物料号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">物料描述
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*胎胚编码
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">胎胚描述
+</t>
+  </si>
+  <si>
+    <t>结构</t>
+  </si>
+  <si>
+    <t>合计余量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">胎胚库存
+</t>
+  </si>
+  <si>
+    <t>胶囊次数L/R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">硫化班产
+</t>
+  </si>
+  <si>
+    <t>早班 Ca sáng {shiftDate1}</t>
+  </si>
+  <si>
+    <t>中班 Ca chiều {shiftDate2}</t>
+  </si>
+  <si>
+    <t>夜班 Ca đêm {shiftDate3}</t>
+  </si>
+  <si>
+    <t>早班 Ca sáng {shiftDate4}</t>
+  </si>
+  <si>
+    <t>中班 Ca chiều {shiftDate5}</t>
+  </si>
+  <si>
+    <t>夜班 Ca đêm {shiftDate6}</t>
+  </si>
+  <si>
+    <t>早班 Ca sáng {shiftDate7}</t>
+  </si>
+  <si>
+    <t>中班 Ca chiều {shiftDate8}</t>
+  </si>
+  <si>
+    <t>对应成型机台号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月计划订单总量
+</t>
+  </si>
+  <si>
+    <t>本月硫化产量（今天夜班）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">备注
+</t>
+  </si>
+  <si>
+    <t>计划
+Kế hoạch</t>
+  </si>
+  <si>
+    <t>实际
+Thực tế</t>
+  </si>
+  <si>
+    <t>Tổng</t>
+  </si>
+  <si>
+    <t>Máy</t>
+  </si>
+  <si>
+    <t>Mã NC</t>
+  </si>
+  <si>
+    <t>Quy cách lưu hóa</t>
+  </si>
+  <si>
+    <t>Mã vật liệu</t>
+  </si>
+  <si>
+    <t>Phôi thành hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUY CÁCH </t>
+  </si>
+  <si>
+    <t>Số còn thiếu</t>
+  </si>
+  <si>
+    <t>Phôi tồn</t>
+  </si>
+  <si>
+    <t>Số lần sử dụng phao L/R</t>
+  </si>
+  <si>
+    <t>Lưu hóa trong ca</t>
+  </si>
+  <si>
+    <t>*顺序
+Stt</t>
+  </si>
+  <si>
+    <t>*计划
+Kế hoạch</t>
+  </si>
+  <si>
+    <t>左右模
+Khuôn trái phải</t>
+  </si>
+  <si>
+    <t>类型
+Loại hình</t>
+  </si>
+  <si>
+    <t>*示方类型
+Phương thức</t>
+  </si>
+  <si>
+    <t>*备注
+Chú ý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*DOT DOT
+</t>
+  </si>
+  <si>
+    <t>Tương ứng máy TH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đơn hàng </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sản lượng lưu hóa đạt </t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>{.sameMaterialPlanQtyTotal}</t>
+  </si>
+  <si>
+    <t>{.nightPlanQtyTotal}</t>
+  </si>
+  <si>
+    <t>{.nightFinishQtyTotal}</t>
+  </si>
+  <si>
+    <t>{.totalPlanQtyFormula}</t>
+  </si>
+  <si>
+    <t>{.lhMachineCode}</t>
+  </si>
+  <si>
+    <t>{.materialCode}</t>
+  </si>
+  <si>
+    <t>{.materialDesc}</t>
+  </si>
+  <si>
+    <t>{.embryoCode}</t>
+  </si>
+  <si>
+    <t>{.mainMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{.structureName}</t>
+  </si>
+  <si>
+    <t>{.dailyPlanQty}</t>
+  </si>
+  <si>
+    <t>{.embryoStock}</t>
+  </si>
+  <si>
+    <t>{.replaceCapsuleCountLeftRight}</t>
+  </si>
+  <si>
+    <t>{.singleMouldShiftQty}</t>
+  </si>
+  <si>
+    <t>{.class1Order}</t>
+  </si>
+  <si>
+    <t>{.class1PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class1FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class1LeftRightMould}</t>
+  </si>
+  <si>
+    <t>{.class1IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class1LhType}</t>
+  </si>
+  <si>
+    <t>{.class1Analysis}</t>
+  </si>
+  <si>
+    <t>{.class1Dot}</t>
+  </si>
+  <si>
+    <t>{.class2Order}</t>
+  </si>
+  <si>
+    <t>{.class2PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class2FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class2LeftRightMould}</t>
+  </si>
+  <si>
+    <t>{.class2IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class2LhType}</t>
+  </si>
+  <si>
+    <t>{.class2Analysis}</t>
+  </si>
+  <si>
+    <t>{.class2Dot}</t>
+  </si>
+  <si>
+    <t>{.class3Order}</t>
+  </si>
+  <si>
+    <t>{.class3PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class3FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class3LeftRightMould}</t>
+  </si>
+  <si>
+    <t>{.class3IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class3LhType}</t>
+  </si>
+  <si>
+    <t>{.class3Analysis}</t>
+  </si>
+  <si>
+    <t>{.class3Dot}</t>
+  </si>
+  <si>
+    <t>{.class4Order}</t>
+  </si>
+  <si>
+    <t>{.class4PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class4FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class4LeftRightMould}</t>
+  </si>
+  <si>
+    <t>{.class4IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class4LhType}</t>
+  </si>
+  <si>
+    <t>{.class4Analysis}</t>
+  </si>
+  <si>
+    <t>{.class4Dot}</t>
+  </si>
+  <si>
+    <t>{.class5Order}</t>
+  </si>
+  <si>
+    <t>{.class5PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class5FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class5LeftRightMould}</t>
+  </si>
+  <si>
+    <t>{.class5IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class5LhType}</t>
+  </si>
+  <si>
+    <t>{.class5Analysis}</t>
+  </si>
+  <si>
+    <t>{.class5Dot}</t>
+  </si>
+  <si>
+    <t>{.class6Order}</t>
+  </si>
+  <si>
+    <t>{.class6PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class6FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class6LeftRightMould}</t>
+  </si>
+  <si>
+    <t>{.class6IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class6LhType}</t>
+  </si>
+  <si>
+    <t>{.class6Analysis}</t>
+  </si>
+  <si>
+    <t>{.class6Dot}</t>
+  </si>
+  <si>
+    <t>{.class7Order}</t>
+  </si>
+  <si>
+    <t>{.class7PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class7FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class7LeftRightMould}</t>
+  </si>
+  <si>
+    <t>{.class7IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class7LhType}</t>
+  </si>
+  <si>
+    <t>{.class7Analysis}</t>
+  </si>
+  <si>
+    <t>{.class7Dot}</t>
+  </si>
+  <si>
+    <t>{.class8Order}</t>
+  </si>
+  <si>
+    <t>{.class8PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class8FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class8LeftRightMould}</t>
+  </si>
+  <si>
+    <t>{.class8IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class8LhType}</t>
+  </si>
+  <si>
+    <t>{.class8Analysis}</t>
+  </si>
+  <si>
+    <t>{.class8Dot}</t>
+  </si>
+  <si>
+    <t>{.cxMachineCode}</t>
+  </si>
+  <si>
+    <t>{.totalDailyPlanQty}</t>
+  </si>
+  <si>
+    <t>{.todayNightFinishQty}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{seq}</t>
+  </si>
+  <si>
+    <t>{planDate}</t>
+  </si>
+  <si>
+    <t>{classIndex}</t>
+  </si>
+  <si>
+    <t>{lhMachineCode}</t>
+  </si>
+  <si>
+    <t>{leftRightMould}</t>
+  </si>
+  <si>
+    <t>{beforeMaterialCode}</t>
+  </si>
+  <si>
+    <t>{beforeMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{afterMaterialCode}</t>
+  </si>
+  <si>
+    <t>{afterMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{afterMaterialType}</t>
+  </si>
+  <si>
+    <t>{changeType}</t>
+  </si>
+  <si>
+    <t>{isDryIceClean}</t>
+  </si>
+  <si>
+    <t>{isSandblastingClean}</t>
+  </si>
+  <si>
+    <t>{isReplaceBlock}</t>
+  </si>
+  <si>
+    <t>{mouldCode}</t>
+  </si>
+  <si>
+    <t>{remark}</t>
+  </si>
+  <si>
+    <t>{title}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">序号
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">计划日期
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">班次
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机台
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">左右模
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当前物料
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">计划物料 
+</t>
+  </si>
+  <si>
+    <t>示方类型</t>
+  </si>
+  <si>
+    <t>按时间下机</t>
+  </si>
+  <si>
+    <t>干冰清洗</t>
+  </si>
+  <si>
+    <t>喷砂清洗</t>
+  </si>
+  <si>
+    <t>只换活字块</t>
+  </si>
+  <si>
+    <t>模具号</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>Ngày tháng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca thay </t>
+  </si>
+  <si>
+    <t>Trái phải của khuôn</t>
+  </si>
+  <si>
+    <t>Mã liệu kế hoạch  đang lưu hóa (trước khi thay)</t>
+  </si>
+  <si>
+    <t>Mô tả vật liệu (trước khi thay)</t>
+  </si>
+  <si>
+    <t>Mã liệu kế hoạch  (sau khi thay)</t>
+  </si>
+  <si>
+    <t>Mô tả vật liệu (sau khi thay)</t>
+  </si>
+  <si>
+    <t>Loại phương thức</t>
+  </si>
+  <si>
+    <t>Xuống máy theo thời gian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vệ sinh đá </t>
+  </si>
+  <si>
+    <t>Vệ sinh cát （VSC）</t>
+  </si>
+  <si>
+    <t>Chỉ thay lắc</t>
+  </si>
+  <si>
+    <t>Mã số khuôn （MSK）</t>
+  </si>
+  <si>
+    <t>{.seq}</t>
+  </si>
+  <si>
+    <t>{.planDate}</t>
+  </si>
+  <si>
+    <t>{.classIndex}</t>
+  </si>
+  <si>
+    <t>{.leftRightMould}</t>
+  </si>
+  <si>
+    <t>{.beforeMaterialCode}</t>
+  </si>
+  <si>
+    <t>{.beforeMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{.afterMaterialCode}</t>
+  </si>
+  <si>
+    <t>{.afterMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{.afterMaterialType}</t>
+  </si>
+  <si>
+    <t>{.endType}</t>
+  </si>
+  <si>
+    <t>{.isDryIceClean}</t>
+  </si>
+  <si>
+    <t>{.isSandblastingClean}</t>
+  </si>
+  <si>
+    <t>{.isReplaceBlock}</t>
+  </si>
+  <si>
+    <t>{.mouldCode}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="10">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="178" formatCode="[$-10804]0;\(0\)"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="m/d;@"/>
-    <numFmt numFmtId="181" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="m/d;@"/>
+    <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="179" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="40">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1069,47 +1168,51 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1117,21 +1220,191 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1139,49 +1412,23 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1212,8 +1459,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1283,38 +1716,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -1337,88 +1740,389 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="13">
+  <cellStyleXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="180" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="37" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="37" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1428,120 +2132,96 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="13">
-    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 12 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 20 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 91" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+  <cellStyles count="61">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="常规 2 5" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="千位分隔 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="千位分隔 3 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Comma 2" xfId="49"/>
+    <cellStyle name="Excel Built-in Normal" xfId="50"/>
+    <cellStyle name="Normal 10" xfId="51"/>
+    <cellStyle name="Normal 12 3" xfId="52"/>
+    <cellStyle name="Normal 2 2" xfId="53"/>
+    <cellStyle name="Normal 20 3" xfId="54"/>
+    <cellStyle name="Normal 91" xfId="55"/>
+    <cellStyle name="Percent 2" xfId="56"/>
+    <cellStyle name="常规 2" xfId="57"/>
+    <cellStyle name="常规 2 5" xfId="58"/>
+    <cellStyle name="千位分隔 3" xfId="59"/>
+    <cellStyle name="千位分隔 3 3" xfId="60"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1560,15 +2240,12 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1584,26 +2261,20 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="61595" y="0"/>
+          <a:off x="433070" y="0"/>
           <a:ext cx="900430" cy="474980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1622,7 +2293,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1638,19 +2309,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -1957,17 +2622,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CD6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="4" width="5.625" customWidth="1"/>
@@ -1999,10 +2663,10 @@
     <col min="79" max="79" width="9.625" customWidth="1"/>
     <col min="80" max="80" width="7.625" customWidth="1"/>
     <col min="81" max="81" width="9.625" customWidth="1"/>
-    <col min="82" max="82" width="37.625" style="50" customWidth="1"/>
+    <col min="82" max="82" width="37.625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" hidden="1" x14ac:dyDescent="0.15">
+    <row r="1" hidden="1" spans="1:82">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2246,103 +2910,103 @@
       <c r="CC1" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="50" t="s">
+      <c r="CD1" s="18" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:82" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="42" t="s">
-        <v>272</v>
-      </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="10" t="s">
+    <row r="2" ht="37.5" customHeight="1" spans="1:82">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="9"/>
-      <c r="AN2" s="9"/>
-      <c r="AO2" s="9"/>
-      <c r="AP2" s="9"/>
-      <c r="AQ2" s="9"/>
-      <c r="AR2" s="9"/>
-      <c r="AS2" s="9"/>
-      <c r="AT2" s="9"/>
-      <c r="AU2" s="9"/>
-      <c r="AV2" s="9"/>
-      <c r="AW2" s="9"/>
-      <c r="AX2" s="9"/>
-      <c r="AY2" s="9"/>
-      <c r="AZ2" s="9"/>
-      <c r="BA2" s="9"/>
-      <c r="BB2" s="11"/>
-      <c r="BC2" s="9"/>
-      <c r="BD2" s="9"/>
-      <c r="BE2" s="9"/>
-      <c r="BF2" s="9"/>
-      <c r="BG2" s="9"/>
-      <c r="BH2" s="9"/>
-      <c r="BI2" s="9"/>
-      <c r="BJ2" s="9"/>
-      <c r="BK2" s="9"/>
-      <c r="BL2" s="9"/>
-      <c r="BM2" s="9"/>
-      <c r="BN2" s="9"/>
-      <c r="BO2" s="9"/>
-      <c r="BP2" s="9"/>
-      <c r="BQ2" s="9"/>
-      <c r="BR2" s="9"/>
-      <c r="BS2" s="9"/>
-      <c r="BT2" s="9"/>
-      <c r="BU2" s="9"/>
-      <c r="BV2" s="9"/>
-      <c r="BW2" s="9"/>
-      <c r="BX2" s="9"/>
-      <c r="BY2" s="9"/>
-      <c r="BZ2" s="9"/>
-      <c r="CA2" s="9"/>
-      <c r="CB2" s="11"/>
-      <c r="CC2" s="11"/>
-      <c r="CD2" s="51"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="19"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="19"/>
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
+      <c r="AG2" s="19"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="19"/>
+      <c r="AP2" s="19"/>
+      <c r="AQ2" s="19"/>
+      <c r="AR2" s="19"/>
+      <c r="AS2" s="19"/>
+      <c r="AT2" s="19"/>
+      <c r="AU2" s="19"/>
+      <c r="AV2" s="19"/>
+      <c r="AW2" s="19"/>
+      <c r="AX2" s="19"/>
+      <c r="AY2" s="19"/>
+      <c r="AZ2" s="19"/>
+      <c r="BA2" s="19"/>
+      <c r="BB2" s="23"/>
+      <c r="BC2" s="19"/>
+      <c r="BD2" s="19"/>
+      <c r="BE2" s="19"/>
+      <c r="BF2" s="19"/>
+      <c r="BG2" s="19"/>
+      <c r="BH2" s="19"/>
+      <c r="BI2" s="19"/>
+      <c r="BJ2" s="19"/>
+      <c r="BK2" s="19"/>
+      <c r="BL2" s="19"/>
+      <c r="BM2" s="19"/>
+      <c r="BN2" s="19"/>
+      <c r="BO2" s="19"/>
+      <c r="BP2" s="19"/>
+      <c r="BQ2" s="19"/>
+      <c r="BR2" s="19"/>
+      <c r="BS2" s="19"/>
+      <c r="BT2" s="19"/>
+      <c r="BU2" s="19"/>
+      <c r="BV2" s="19"/>
+      <c r="BW2" s="19"/>
+      <c r="BX2" s="19"/>
+      <c r="BY2" s="19"/>
+      <c r="BZ2" s="19"/>
+      <c r="CA2" s="19"/>
+      <c r="CB2" s="23"/>
+      <c r="CC2" s="23"/>
+      <c r="CD2" s="24"/>
     </row>
-    <row r="3" spans="1:82" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" ht="16.9" customHeight="1" spans="1:82">
       <c r="B3" s="25">
         <f>SUM(B6:B108139)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="12"/>
+      <c r="C3" s="26"/>
       <c r="D3" s="25">
         <f>SUM(D6:D108139)</f>
         <v>0</v>
@@ -2353,24 +3017,24 @@
       <c r="H3" s="25"/>
       <c r="I3" s="25"/>
       <c r="J3" s="25"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26">
+      <c r="K3" s="27"/>
+      <c r="L3" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27">
         <f>SUM(P6:P108139)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
       <c r="S3" s="25"/>
       <c r="T3" s="25"/>
       <c r="U3" s="25"/>
       <c r="V3" s="25"/>
-      <c r="W3" s="28"/>
+      <c r="W3" s="30"/>
       <c r="X3" s="25">
         <f>SUM(X6:X108139)</f>
         <v>0</v>
@@ -2378,7 +3042,7 @@
       <c r="Y3" s="25"/>
       <c r="Z3" s="25"/>
       <c r="AA3" s="25"/>
-      <c r="AB3" s="28"/>
+      <c r="AB3" s="30"/>
       <c r="AC3" s="25"/>
       <c r="AD3" s="25"/>
       <c r="AE3" s="25"/>
@@ -2386,12 +3050,12 @@
         <f>SUM(AF6:AF108139)</f>
         <v>0</v>
       </c>
-      <c r="AG3" s="28"/>
+      <c r="AG3" s="30"/>
       <c r="AH3" s="25"/>
       <c r="AI3" s="25"/>
       <c r="AJ3" s="25"/>
       <c r="AK3" s="25"/>
-      <c r="AL3" s="28"/>
+      <c r="AL3" s="30"/>
       <c r="AM3" s="25"/>
       <c r="AN3" s="25">
         <f>SUM(AN6:AN108139)</f>
@@ -2399,12 +3063,12 @@
       </c>
       <c r="AO3" s="25"/>
       <c r="AP3" s="25"/>
-      <c r="AQ3" s="28"/>
+      <c r="AQ3" s="30"/>
       <c r="AR3" s="25"/>
       <c r="AS3" s="25"/>
       <c r="AT3" s="25"/>
       <c r="AU3" s="25"/>
-      <c r="AV3" s="28">
+      <c r="AV3" s="30">
         <f>SUM(AV6:AV108139)</f>
         <v>0</v>
       </c>
@@ -2412,7 +3076,7 @@
       <c r="AX3" s="25"/>
       <c r="AY3" s="25"/>
       <c r="AZ3" s="25"/>
-      <c r="BA3" s="28"/>
+      <c r="BA3" s="30"/>
       <c r="BB3" s="25"/>
       <c r="BC3" s="25"/>
       <c r="BD3" s="25">
@@ -2420,940 +3084,942 @@
         <v>0</v>
       </c>
       <c r="BE3" s="25"/>
-      <c r="BF3" s="28"/>
-      <c r="BG3" s="26"/>
-      <c r="BH3" s="26"/>
-      <c r="BI3" s="26"/>
-      <c r="BJ3" s="12"/>
-      <c r="BK3" s="13"/>
+      <c r="BF3" s="30"/>
+      <c r="BG3" s="27"/>
+      <c r="BH3" s="27"/>
+      <c r="BI3" s="27"/>
+      <c r="BJ3" s="26"/>
+      <c r="BK3" s="31"/>
       <c r="BL3" s="25">
         <f>SUM(BL6:BL108139)</f>
         <v>0</v>
       </c>
-      <c r="BM3" s="12"/>
-      <c r="BN3" s="12"/>
-      <c r="BO3" s="12"/>
-      <c r="BP3" s="12"/>
-      <c r="BQ3" s="12"/>
-      <c r="BR3" s="12"/>
-      <c r="BS3" s="12"/>
+      <c r="BM3" s="26"/>
+      <c r="BN3" s="26"/>
+      <c r="BO3" s="26"/>
+      <c r="BP3" s="26"/>
+      <c r="BQ3" s="26"/>
+      <c r="BR3" s="26"/>
+      <c r="BS3" s="26"/>
       <c r="BT3" s="25">
         <f>SUM(BT6:BT108139)</f>
         <v>0</v>
       </c>
-      <c r="BU3" s="12"/>
-      <c r="BV3" s="12"/>
-      <c r="BW3" s="12"/>
-      <c r="BX3" s="12"/>
-      <c r="BY3" s="12"/>
-      <c r="BZ3" s="12"/>
-      <c r="CA3" s="29"/>
-      <c r="CB3" s="12"/>
-      <c r="CC3" s="12"/>
-      <c r="CD3" s="52"/>
+      <c r="BU3" s="26"/>
+      <c r="BV3" s="26"/>
+      <c r="BW3" s="26"/>
+      <c r="BX3" s="26"/>
+      <c r="BY3" s="26"/>
+      <c r="BZ3" s="26"/>
+      <c r="CA3" s="32"/>
+      <c r="CB3" s="26"/>
+      <c r="CC3" s="26"/>
+      <c r="CD3" s="33"/>
     </row>
-    <row r="4" spans="1:82" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="14" t="s">
+    <row r="4" ht="36" customHeight="1" spans="1:82">
+      <c r="B4" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="C4" s="35"/>
+      <c r="D4" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="G4" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="H4" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="I4" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="J4" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="K4" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="L4" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="N4" s="14" t="s">
+      <c r="M4" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="O4" s="47" t="s">
+      <c r="N4" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="45"/>
-      <c r="T4" s="45"/>
-      <c r="U4" s="45"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="47" t="s">
+      <c r="O4" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="X4" s="45"/>
-      <c r="Y4" s="45"/>
-      <c r="Z4" s="45"/>
-      <c r="AA4" s="45"/>
-      <c r="AB4" s="45"/>
-      <c r="AC4" s="45"/>
-      <c r="AD4" s="46"/>
-      <c r="AE4" s="49" t="s">
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="AF4" s="45"/>
-      <c r="AG4" s="45"/>
-      <c r="AH4" s="45"/>
-      <c r="AI4" s="45"/>
-      <c r="AJ4" s="45"/>
-      <c r="AK4" s="45"/>
-      <c r="AL4" s="46"/>
-      <c r="AM4" s="49" t="s">
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="AN4" s="45"/>
-      <c r="AO4" s="45"/>
-      <c r="AP4" s="45"/>
-      <c r="AQ4" s="45"/>
-      <c r="AR4" s="45"/>
-      <c r="AS4" s="45"/>
-      <c r="AT4" s="46"/>
-      <c r="AU4" s="49" t="s">
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="38"/>
+      <c r="AK4" s="38"/>
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="AV4" s="45"/>
-      <c r="AW4" s="45"/>
-      <c r="AX4" s="45"/>
-      <c r="AY4" s="45"/>
-      <c r="AZ4" s="45"/>
-      <c r="BA4" s="45"/>
-      <c r="BB4" s="46"/>
-      <c r="BC4" s="44" t="s">
+      <c r="AN4" s="38"/>
+      <c r="AO4" s="38"/>
+      <c r="AP4" s="38"/>
+      <c r="AQ4" s="38"/>
+      <c r="AR4" s="38"/>
+      <c r="AS4" s="38"/>
+      <c r="AT4" s="35"/>
+      <c r="AU4" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="BD4" s="45"/>
-      <c r="BE4" s="45"/>
-      <c r="BF4" s="45"/>
-      <c r="BG4" s="45"/>
-      <c r="BH4" s="45"/>
-      <c r="BI4" s="45"/>
-      <c r="BJ4" s="46"/>
-      <c r="BK4" s="44" t="s">
+      <c r="AV4" s="38"/>
+      <c r="AW4" s="38"/>
+      <c r="AX4" s="38"/>
+      <c r="AY4" s="38"/>
+      <c r="AZ4" s="38"/>
+      <c r="BA4" s="38"/>
+      <c r="BB4" s="35"/>
+      <c r="BC4" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="BL4" s="45"/>
-      <c r="BM4" s="45"/>
-      <c r="BN4" s="45"/>
-      <c r="BO4" s="45"/>
-      <c r="BP4" s="45"/>
-      <c r="BQ4" s="45"/>
-      <c r="BR4" s="46"/>
-      <c r="BS4" s="44" t="s">
+      <c r="BD4" s="38"/>
+      <c r="BE4" s="38"/>
+      <c r="BF4" s="38"/>
+      <c r="BG4" s="38"/>
+      <c r="BH4" s="38"/>
+      <c r="BI4" s="38"/>
+      <c r="BJ4" s="35"/>
+      <c r="BK4" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="BT4" s="45"/>
-      <c r="BU4" s="45"/>
-      <c r="BV4" s="45"/>
-      <c r="BW4" s="45"/>
-      <c r="BX4" s="45"/>
-      <c r="BY4" s="45"/>
-      <c r="BZ4" s="46"/>
-      <c r="CA4" s="14" t="s">
+      <c r="BL4" s="38"/>
+      <c r="BM4" s="38"/>
+      <c r="BN4" s="38"/>
+      <c r="BO4" s="38"/>
+      <c r="BP4" s="38"/>
+      <c r="BQ4" s="38"/>
+      <c r="BR4" s="35"/>
+      <c r="BS4" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="CB4" s="14" t="s">
+      <c r="BT4" s="38"/>
+      <c r="BU4" s="38"/>
+      <c r="BV4" s="38"/>
+      <c r="BW4" s="38"/>
+      <c r="BX4" s="38"/>
+      <c r="BY4" s="38"/>
+      <c r="BZ4" s="35"/>
+      <c r="CA4" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="CC4" s="14" t="s">
+      <c r="CB4" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="CD4" s="14" t="s">
+      <c r="CC4" s="36" t="s">
         <v>107</v>
       </c>
+      <c r="CD4" s="36" t="s">
+        <v>108</v>
+      </c>
     </row>
-    <row r="5" spans="1:82" ht="48" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="23" t="s">
+    <row r="5" ht="48" customHeight="1" spans="1:82">
+      <c r="B5" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="E5" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="G5" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="H5" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="J5" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="L5" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="M5" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="O5" s="24" t="s">
+      <c r="N5" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="P5" s="24" t="s">
+      <c r="O5" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="Q5" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="R5" s="24" t="s">
+      <c r="P5" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="S5" s="24" t="s">
+      <c r="Q5" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="R5" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="T5" s="24" t="s">
+      <c r="S5" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="U5" s="24" t="s">
+      <c r="T5" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="V5" s="24" t="s">
+      <c r="U5" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="W5" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="X5" s="24" t="s">
+      <c r="V5" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="W5" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="Y5" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z5" s="24" t="s">
+      <c r="X5" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="AA5" s="24" t="s">
+      <c r="Y5" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z5" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="AB5" s="24" t="s">
+      <c r="AA5" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="AC5" s="24" t="s">
+      <c r="AB5" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="AD5" s="24" t="s">
+      <c r="AC5" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="AE5" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF5" s="16" t="s">
+      <c r="AD5" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE5" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="AG5" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="AH5" s="16" t="s">
+      <c r="AF5" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="AI5" s="16" t="s">
+      <c r="AG5" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH5" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="AJ5" s="16" t="s">
+      <c r="AI5" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="AK5" s="16" t="s">
+      <c r="AJ5" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="AL5" s="16" t="s">
+      <c r="AK5" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="AM5" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="AN5" s="16" t="s">
+      <c r="AL5" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM5" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="AO5" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP5" s="16" t="s">
+      <c r="AN5" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="AQ5" s="16" t="s">
+      <c r="AO5" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP5" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="AR5" s="16" t="s">
+      <c r="AQ5" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="AS5" s="16" t="s">
+      <c r="AR5" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="AT5" s="16" t="s">
+      <c r="AS5" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="AU5" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="AV5" s="16" t="s">
+      <c r="AT5" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="AU5" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="AW5" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="AX5" s="16" t="s">
+      <c r="AV5" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="AY5" s="16" t="s">
+      <c r="AW5" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX5" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="AZ5" s="16" t="s">
+      <c r="AY5" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="BA5" s="16" t="s">
+      <c r="AZ5" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="BB5" s="16" t="s">
+      <c r="BA5" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="BC5" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="BD5" s="17" t="s">
+      <c r="BB5" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="BC5" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="BE5" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="BF5" s="17" t="s">
+      <c r="BD5" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="BG5" s="17" t="s">
+      <c r="BE5" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="BF5" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="BH5" s="17" t="s">
+      <c r="BG5" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="BI5" s="17" t="s">
+      <c r="BH5" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="BJ5" s="17" t="s">
+      <c r="BI5" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="BK5" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="BL5" s="17" t="s">
+      <c r="BJ5" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK5" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="BM5" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="BN5" s="17" t="s">
+      <c r="BL5" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="BO5" s="17" t="s">
+      <c r="BM5" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="BN5" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="BP5" s="17" t="s">
+      <c r="BO5" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="BQ5" s="17" t="s">
+      <c r="BP5" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="BR5" s="17" t="s">
+      <c r="BQ5" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="BS5" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="BT5" s="17" t="s">
+      <c r="BR5" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS5" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="BU5" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="BV5" s="17" t="s">
+      <c r="BT5" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="BW5" s="17" t="s">
+      <c r="BU5" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="BV5" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="BX5" s="17" t="s">
+      <c r="BW5" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="BY5" s="17" t="s">
+      <c r="BX5" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="BZ5" s="17" t="s">
+      <c r="BY5" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="CA5" s="15" t="s">
+      <c r="BZ5" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="CB5" s="15" t="s">
+      <c r="CA5" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="CC5" s="15" t="s">
+      <c r="CB5" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="CD5" s="15" t="s">
+      <c r="CC5" s="41" t="s">
         <v>131</v>
       </c>
+      <c r="CD5" s="41" t="s">
+        <v>132</v>
+      </c>
     </row>
-    <row r="6" spans="1:82" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="30" t="s">
+    <row r="6" s="17" customFormat="1" ht="58.15" spans="1:82">
+      <c r="A6" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="C6" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="D6" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="E6" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="F6" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="G6" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="H6" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="I6" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="J6" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="K6" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="M6" s="21" t="s">
+      <c r="L6" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="N6" s="22" t="s">
+      <c r="M6" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="O6" s="31" t="s">
+      <c r="N6" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="P6" s="30" t="s">
+      <c r="O6" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="Q6" s="30" t="s">
+      <c r="P6" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="R6" s="30" t="s">
+      <c r="Q6" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="S6" s="30" t="s">
+      <c r="R6" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="T6" s="30" t="s">
+      <c r="S6" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="U6" s="30" t="s">
+      <c r="T6" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="V6" s="30" t="s">
+      <c r="U6" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="W6" s="30" t="s">
+      <c r="V6" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="X6" s="30" t="s">
+      <c r="W6" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="Y6" s="30" t="s">
+      <c r="X6" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="Z6" s="30" t="s">
+      <c r="Y6" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="AA6" s="30" t="s">
+      <c r="Z6" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="AB6" s="30" t="s">
+      <c r="AA6" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="AC6" s="30" t="s">
+      <c r="AB6" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="AD6" s="30" t="s">
+      <c r="AC6" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="AE6" s="30" t="s">
+      <c r="AD6" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="AF6" s="30" t="s">
+      <c r="AE6" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="AG6" s="30" t="s">
+      <c r="AF6" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="AH6" s="30" t="s">
+      <c r="AG6" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="AI6" s="30" t="s">
+      <c r="AH6" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="AJ6" s="30" t="s">
+      <c r="AI6" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="AK6" s="30" t="s">
+      <c r="AJ6" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="AL6" s="30" t="s">
+      <c r="AK6" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="AM6" s="30" t="s">
+      <c r="AL6" s="48" t="s">
         <v>170</v>
       </c>
-      <c r="AN6" s="30" t="s">
+      <c r="AM6" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="AO6" s="30" t="s">
+      <c r="AN6" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="AP6" s="30" t="s">
+      <c r="AO6" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="AQ6" s="30" t="s">
+      <c r="AP6" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="AR6" s="30" t="s">
+      <c r="AQ6" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="AS6" s="30" t="s">
+      <c r="AR6" s="49" t="s">
         <v>176</v>
       </c>
-      <c r="AT6" s="30" t="s">
+      <c r="AS6" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="AU6" s="30" t="s">
+      <c r="AT6" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="AV6" s="30" t="s">
+      <c r="AU6" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="AW6" s="30" t="s">
+      <c r="AV6" s="48" t="s">
         <v>180</v>
       </c>
-      <c r="AX6" s="30" t="s">
+      <c r="AW6" s="49" t="s">
         <v>181</v>
       </c>
-      <c r="AY6" s="30" t="s">
+      <c r="AX6" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="AZ6" s="30" t="s">
+      <c r="AY6" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="BA6" s="30" t="s">
+      <c r="AZ6" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="BB6" s="30" t="s">
+      <c r="BA6" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="BC6" s="30" t="s">
+      <c r="BB6" s="49" t="s">
         <v>186</v>
       </c>
-      <c r="BD6" s="30" t="s">
+      <c r="BC6" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="BE6" s="30" t="s">
+      <c r="BD6" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="BF6" s="30" t="s">
+      <c r="BE6" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="BG6" s="30" t="s">
+      <c r="BF6" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="BH6" s="30" t="s">
+      <c r="BG6" s="50" t="s">
         <v>191</v>
       </c>
-      <c r="BI6" s="30" t="s">
+      <c r="BH6" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="BJ6" s="30" t="s">
+      <c r="BI6" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="BK6" s="30" t="s">
+      <c r="BJ6" s="49" t="s">
         <v>194</v>
       </c>
-      <c r="BL6" s="30" t="s">
+      <c r="BK6" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="BM6" s="30" t="s">
+      <c r="BL6" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="BN6" s="30" t="s">
+      <c r="BM6" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="BO6" s="30" t="s">
+      <c r="BN6" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="BP6" s="30" t="s">
+      <c r="BO6" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="BQ6" s="30" t="s">
+      <c r="BP6" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="BR6" s="30" t="s">
+      <c r="BQ6" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="BS6" s="30" t="s">
+      <c r="BR6" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="BT6" s="30" t="s">
+      <c r="BS6" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="BU6" s="30" t="s">
+      <c r="BT6" s="51" t="s">
         <v>204</v>
       </c>
-      <c r="BV6" s="30" t="s">
+      <c r="BU6" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="BW6" s="30" t="s">
+      <c r="BV6" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="BX6" s="30" t="s">
+      <c r="BW6" s="51" t="s">
         <v>207</v>
       </c>
-      <c r="BY6" s="30" t="s">
+      <c r="BX6" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="BZ6" s="32" t="s">
+      <c r="BY6" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="CA6" s="33" t="s">
+      <c r="BZ6" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="CB6" s="33" t="s">
+      <c r="CA6" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="CC6" s="19" t="s">
+      <c r="CB6" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="CD6" s="21" t="s">
+      <c r="CC6" s="51" t="s">
         <v>213</v>
+      </c>
+      <c r="CD6" s="51" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="E2:I2"/>
-    <mergeCell ref="BS4:BZ4"/>
+    <mergeCell ref="B4:C4"/>
     <mergeCell ref="O4:V4"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="AM4:AT4"/>
     <mergeCell ref="W4:AD4"/>
     <mergeCell ref="AE4:AL4"/>
+    <mergeCell ref="AM4:AT4"/>
     <mergeCell ref="AU4:BB4"/>
+    <mergeCell ref="BC4:BJ4"/>
     <mergeCell ref="BK4:BR4"/>
-    <mergeCell ref="BC4:BJ4"/>
+    <mergeCell ref="BS4:BZ4"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="G3:H3">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5 AA5 AI5 AQ5 AY5 BG5 BO5 BW5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5 AA5 AI5 AQ5 AY5 BG5 BO5 BW5">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.6" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
-    <col min="3" max="4" width="5.625" style="34" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="34" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="34.125" style="35" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.125" style="35" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="35" customWidth="1"/>
-    <col min="11" max="11" width="5.75" style="35" customWidth="1"/>
-    <col min="12" max="14" width="5.75" style="34" customWidth="1"/>
-    <col min="15" max="15" width="27.375" style="34" customWidth="1"/>
-    <col min="16" max="16" width="9" style="34" customWidth="1"/>
-    <col min="17" max="17" width="8" style="34" customWidth="1"/>
-    <col min="18" max="16384" width="8" style="34"/>
+    <col min="1" max="1" width="3" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="3" customWidth="1"/>
+    <col min="3" max="4" width="5.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="34.125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="5" customWidth="1"/>
+    <col min="11" max="11" width="5.75" style="5" customWidth="1"/>
+    <col min="12" max="14" width="5.75" style="4" customWidth="1"/>
+    <col min="15" max="15" width="27.375" style="4" customWidth="1"/>
+    <col min="16" max="16" width="9" style="4" customWidth="1"/>
+    <col min="17" max="17" width="8" style="4" customWidth="1"/>
+    <col min="18" max="16384" width="8" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" hidden="1" spans="1:16">
+      <c r="A1" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" ht="33.75" customHeight="1" spans="1:16">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="34.15" customHeight="1" spans="1:16">
+      <c r="A3" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:16">
+      <c r="A4" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" ht="11.45" customHeight="1" spans="1:16">
+      <c r="A5" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="P5" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G1" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="I1" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="J1" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="K1" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="L1" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="M1" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="N1" s="34" t="s">
-        <v>227</v>
-      </c>
-      <c r="O1" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="P1" s="34" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="3"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="39"/>
-    </row>
-    <row r="3" spans="1:16" s="40" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="40" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="11.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P5" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Company\GIT\jy_aps\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EB800A-B409-4D29-BB0F-D7A3FB210511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555" tabRatio="844"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="1" r:id="rId1"/>
@@ -290,7 +291,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>{yearmonthday}</t>
     </r>
@@ -308,7 +309,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -318,7 +319,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -327,7 +328,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>n k</t>
     </r>
@@ -336,7 +337,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -345,7 +346,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
     </r>
@@ -354,7 +355,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -363,7 +364,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ch s</t>
     </r>
@@ -372,7 +373,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -381,7 +382,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>n xu</t>
     </r>
@@ -390,7 +391,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ấ</t>
     </r>
@@ -399,7 +400,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>t c</t>
     </r>
@@ -408,7 +409,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -417,7 +418,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">a công </t>
     </r>
@@ -426,7 +427,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -435,7 +436,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>o</t>
     </r>
@@ -444,7 +445,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -453,7 +454,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>n l</t>
     </r>
@@ -462,7 +463,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -471,7 +472,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>u hóa toàn thép</t>
     </r>
@@ -482,7 +483,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -500,7 +501,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>phiên bản</t>
     </r>
@@ -518,7 +519,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>{productionVersion}</t>
     </r>
@@ -538,7 +539,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 Tổng kế hoạch</t>
@@ -1146,20 +1147,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="10">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="m/d;@"/>
-    <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="179" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="m/d;@"/>
+    <numFmt numFmtId="180" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="181" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="182" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="183" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1190,7 +1188,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1202,18 +1200,18 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1227,7 +1225,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1238,157 +1236,13 @@
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1400,7 +1254,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1427,8 +1281,19 @@
       <name val="等线"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1459,194 +1324,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1739,322 +1418,80 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="61">
+  <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="37" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="37" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2066,54 +1503,93 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -2123,105 +1599,21 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="61">
+  <cellStyles count="13">
+    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Normal 12 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Normal 20 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Normal 91" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Comma 2" xfId="49"/>
-    <cellStyle name="Excel Built-in Normal" xfId="50"/>
-    <cellStyle name="Normal 10" xfId="51"/>
-    <cellStyle name="Normal 12 3" xfId="52"/>
-    <cellStyle name="Normal 2 2" xfId="53"/>
-    <cellStyle name="Normal 20 3" xfId="54"/>
-    <cellStyle name="Normal 91" xfId="55"/>
-    <cellStyle name="Percent 2" xfId="56"/>
-    <cellStyle name="常规 2" xfId="57"/>
-    <cellStyle name="常规 2 5" xfId="58"/>
-    <cellStyle name="千位分隔 3" xfId="59"/>
-    <cellStyle name="千位分隔 3 3" xfId="60"/>
+    <cellStyle name="常规 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="常规 2 5" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="千位分隔 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔 3 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2240,12 +1632,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -2261,13 +1656,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21"/>
+        <xdr:cNvPr id="2" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2293,7 +1694,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2309,13 +1710,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21"/>
+        <xdr:cNvPr id="2" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
@@ -2622,51 +2029,52 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CD6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="4.875" customWidth="1"/>
-    <col min="2" max="4" width="5.625" customWidth="1"/>
+    <col min="1" max="1" width="4.8984375" customWidth="1"/>
+    <col min="2" max="4" width="5.59765625" customWidth="1"/>
     <col min="5" max="5" width="6.5" customWidth="1"/>
-    <col min="6" max="6" width="9.625" customWidth="1"/>
-    <col min="7" max="7" width="32.625" customWidth="1"/>
+    <col min="6" max="6" width="9.59765625" customWidth="1"/>
+    <col min="7" max="7" width="32.59765625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="12" width="5.625" customWidth="1"/>
-    <col min="13" max="13" width="6.125" customWidth="1"/>
-    <col min="14" max="14" width="5.625" customWidth="1"/>
-    <col min="15" max="15" width="3.125" customWidth="1"/>
-    <col min="16" max="22" width="5.125" customWidth="1"/>
-    <col min="23" max="23" width="3.125" customWidth="1"/>
-    <col min="24" max="30" width="5.125" customWidth="1"/>
-    <col min="31" max="31" width="3.125" customWidth="1"/>
-    <col min="32" max="38" width="5.125" customWidth="1"/>
-    <col min="39" max="39" width="3.125" customWidth="1"/>
-    <col min="40" max="46" width="5.125" customWidth="1"/>
-    <col min="47" max="47" width="3.125" customWidth="1"/>
-    <col min="48" max="54" width="5.125" customWidth="1"/>
-    <col min="55" max="55" width="3.125" customWidth="1"/>
-    <col min="56" max="62" width="5.125" customWidth="1"/>
-    <col min="63" max="63" width="3.125" customWidth="1"/>
-    <col min="64" max="70" width="5.125" customWidth="1"/>
-    <col min="71" max="71" width="3.125" customWidth="1"/>
-    <col min="72" max="78" width="5.125" customWidth="1"/>
-    <col min="79" max="79" width="9.625" customWidth="1"/>
-    <col min="80" max="80" width="7.625" customWidth="1"/>
-    <col min="81" max="81" width="9.625" customWidth="1"/>
-    <col min="82" max="82" width="37.625" style="18" customWidth="1"/>
+    <col min="10" max="10" width="17.09765625" customWidth="1"/>
+    <col min="11" max="12" width="5.59765625" customWidth="1"/>
+    <col min="13" max="13" width="6.09765625" customWidth="1"/>
+    <col min="14" max="14" width="5.59765625" customWidth="1"/>
+    <col min="15" max="15" width="3.09765625" customWidth="1"/>
+    <col min="16" max="22" width="5.09765625" customWidth="1"/>
+    <col min="23" max="23" width="3.09765625" customWidth="1"/>
+    <col min="24" max="30" width="5.09765625" customWidth="1"/>
+    <col min="31" max="31" width="3.09765625" customWidth="1"/>
+    <col min="32" max="38" width="5.09765625" customWidth="1"/>
+    <col min="39" max="39" width="3.09765625" customWidth="1"/>
+    <col min="40" max="46" width="5.09765625" customWidth="1"/>
+    <col min="47" max="47" width="3.09765625" customWidth="1"/>
+    <col min="48" max="54" width="5.09765625" customWidth="1"/>
+    <col min="55" max="55" width="3.09765625" customWidth="1"/>
+    <col min="56" max="62" width="5.09765625" customWidth="1"/>
+    <col min="63" max="63" width="3.09765625" customWidth="1"/>
+    <col min="64" max="70" width="5.09765625" customWidth="1"/>
+    <col min="71" max="71" width="3.09765625" customWidth="1"/>
+    <col min="72" max="78" width="5.09765625" customWidth="1"/>
+    <col min="79" max="79" width="9.59765625" customWidth="1"/>
+    <col min="80" max="80" width="7.59765625" customWidth="1"/>
+    <col min="81" max="81" width="9.59765625" customWidth="1"/>
+    <col min="82" max="82" width="37.59765625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1" spans="1:82">
+    <row r="1" spans="1:82" hidden="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2914,26 +2322,26 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" ht="37.5" customHeight="1" spans="1:82">
+    <row r="2" spans="1:82" ht="37.5" customHeight="1">
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
       <c r="J2" s="17"/>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="20" t="s">
         <v>83</v>
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" s="17"/>
       <c r="O2" s="19"/>
-      <c r="P2" s="23"/>
+      <c r="P2" s="21"/>
       <c r="Q2" s="19"/>
       <c r="R2" s="19"/>
       <c r="S2" s="19"/>
@@ -2971,7 +2379,7 @@
       <c r="AY2" s="19"/>
       <c r="AZ2" s="19"/>
       <c r="BA2" s="19"/>
-      <c r="BB2" s="23"/>
+      <c r="BB2" s="21"/>
       <c r="BC2" s="19"/>
       <c r="BD2" s="19"/>
       <c r="BE2" s="19"/>
@@ -2997,803 +2405,803 @@
       <c r="BY2" s="19"/>
       <c r="BZ2" s="19"/>
       <c r="CA2" s="19"/>
-      <c r="CB2" s="23"/>
-      <c r="CC2" s="23"/>
-      <c r="CD2" s="24"/>
+      <c r="CB2" s="21"/>
+      <c r="CC2" s="21"/>
+      <c r="CD2" s="22"/>
     </row>
-    <row r="3" ht="16.9" customHeight="1" spans="1:82">
-      <c r="B3" s="25">
+    <row r="3" spans="1:82" ht="16.95" customHeight="1">
+      <c r="B3" s="23">
         <f>SUM(B6:B108139)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="25">
+      <c r="C3" s="24"/>
+      <c r="D3" s="23">
         <f>SUM(D6:D108139)</f>
         <v>0</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="28" t="s">
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27">
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25">
         <f>SUM(P6:P108139)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="25">
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="23">
         <f>SUM(X6:X108139)</f>
         <v>0</v>
       </c>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25">
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23">
         <f>SUM(AF6:AF108139)</f>
         <v>0</v>
       </c>
-      <c r="AG3" s="30"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="AL3" s="30"/>
-      <c r="AM3" s="25"/>
-      <c r="AN3" s="25">
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="23"/>
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="23"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23">
         <f>SUM(AN6:AN108139)</f>
         <v>0</v>
       </c>
-      <c r="AO3" s="25"/>
-      <c r="AP3" s="25"/>
-      <c r="AQ3" s="30"/>
-      <c r="AR3" s="25"/>
-      <c r="AS3" s="25"/>
-      <c r="AT3" s="25"/>
-      <c r="AU3" s="25"/>
-      <c r="AV3" s="30">
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="23"/>
+      <c r="AU3" s="23"/>
+      <c r="AV3" s="28">
         <f>SUM(AV6:AV108139)</f>
         <v>0</v>
       </c>
-      <c r="AW3" s="25"/>
-      <c r="AX3" s="25"/>
-      <c r="AY3" s="25"/>
-      <c r="AZ3" s="25"/>
-      <c r="BA3" s="30"/>
-      <c r="BB3" s="25"/>
-      <c r="BC3" s="25"/>
-      <c r="BD3" s="25">
+      <c r="AW3" s="23"/>
+      <c r="AX3" s="23"/>
+      <c r="AY3" s="23"/>
+      <c r="AZ3" s="23"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="23"/>
+      <c r="BC3" s="23"/>
+      <c r="BD3" s="23">
         <f>SUM(BD6:BD108139)</f>
         <v>0</v>
       </c>
-      <c r="BE3" s="25"/>
-      <c r="BF3" s="30"/>
-      <c r="BG3" s="27"/>
-      <c r="BH3" s="27"/>
-      <c r="BI3" s="27"/>
-      <c r="BJ3" s="26"/>
-      <c r="BK3" s="31"/>
-      <c r="BL3" s="25">
+      <c r="BE3" s="23"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="25"/>
+      <c r="BH3" s="25"/>
+      <c r="BI3" s="25"/>
+      <c r="BJ3" s="24"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="23">
         <f>SUM(BL6:BL108139)</f>
         <v>0</v>
       </c>
-      <c r="BM3" s="26"/>
-      <c r="BN3" s="26"/>
-      <c r="BO3" s="26"/>
-      <c r="BP3" s="26"/>
-      <c r="BQ3" s="26"/>
-      <c r="BR3" s="26"/>
-      <c r="BS3" s="26"/>
-      <c r="BT3" s="25">
+      <c r="BM3" s="24"/>
+      <c r="BN3" s="24"/>
+      <c r="BO3" s="24"/>
+      <c r="BP3" s="24"/>
+      <c r="BQ3" s="24"/>
+      <c r="BR3" s="24"/>
+      <c r="BS3" s="24"/>
+      <c r="BT3" s="23">
         <f>SUM(BT6:BT108139)</f>
         <v>0</v>
       </c>
-      <c r="BU3" s="26"/>
-      <c r="BV3" s="26"/>
-      <c r="BW3" s="26"/>
-      <c r="BX3" s="26"/>
-      <c r="BY3" s="26"/>
-      <c r="BZ3" s="26"/>
-      <c r="CA3" s="32"/>
-      <c r="CB3" s="26"/>
-      <c r="CC3" s="26"/>
-      <c r="CD3" s="33"/>
+      <c r="BU3" s="24"/>
+      <c r="BV3" s="24"/>
+      <c r="BW3" s="24"/>
+      <c r="BX3" s="24"/>
+      <c r="BY3" s="24"/>
+      <c r="BZ3" s="24"/>
+      <c r="CA3" s="30"/>
+      <c r="CB3" s="24"/>
+      <c r="CC3" s="24"/>
+      <c r="CD3" s="31"/>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:82">
-      <c r="B4" s="34" t="s">
+    <row r="4" spans="1:82" ht="36" customHeight="1">
+      <c r="B4" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36" t="s">
+      <c r="C4" s="49"/>
+      <c r="D4" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="N4" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="52" t="s">
+      <c r="O4" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="52" t="s">
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="35"/>
-      <c r="AE4" s="39" t="s">
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
+      <c r="AB4" s="51"/>
+      <c r="AC4" s="51"/>
+      <c r="AD4" s="49"/>
+      <c r="AE4" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="39" t="s">
+      <c r="AF4" s="51"/>
+      <c r="AG4" s="51"/>
+      <c r="AH4" s="51"/>
+      <c r="AI4" s="51"/>
+      <c r="AJ4" s="51"/>
+      <c r="AK4" s="51"/>
+      <c r="AL4" s="49"/>
+      <c r="AM4" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="35"/>
-      <c r="AU4" s="39" t="s">
+      <c r="AN4" s="51"/>
+      <c r="AO4" s="51"/>
+      <c r="AP4" s="51"/>
+      <c r="AQ4" s="51"/>
+      <c r="AR4" s="51"/>
+      <c r="AS4" s="51"/>
+      <c r="AT4" s="49"/>
+      <c r="AU4" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="35"/>
-      <c r="BC4" s="40" t="s">
+      <c r="AV4" s="51"/>
+      <c r="AW4" s="51"/>
+      <c r="AX4" s="51"/>
+      <c r="AY4" s="51"/>
+      <c r="AZ4" s="51"/>
+      <c r="BA4" s="51"/>
+      <c r="BB4" s="49"/>
+      <c r="BC4" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
-      <c r="BJ4" s="35"/>
-      <c r="BK4" s="40" t="s">
+      <c r="BD4" s="51"/>
+      <c r="BE4" s="51"/>
+      <c r="BF4" s="51"/>
+      <c r="BG4" s="51"/>
+      <c r="BH4" s="51"/>
+      <c r="BI4" s="51"/>
+      <c r="BJ4" s="49"/>
+      <c r="BK4" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="BL4" s="38"/>
-      <c r="BM4" s="38"/>
-      <c r="BN4" s="38"/>
-      <c r="BO4" s="38"/>
-      <c r="BP4" s="38"/>
-      <c r="BQ4" s="38"/>
-      <c r="BR4" s="35"/>
-      <c r="BS4" s="40" t="s">
+      <c r="BL4" s="51"/>
+      <c r="BM4" s="51"/>
+      <c r="BN4" s="51"/>
+      <c r="BO4" s="51"/>
+      <c r="BP4" s="51"/>
+      <c r="BQ4" s="51"/>
+      <c r="BR4" s="49"/>
+      <c r="BS4" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="BT4" s="38"/>
-      <c r="BU4" s="38"/>
-      <c r="BV4" s="38"/>
-      <c r="BW4" s="38"/>
-      <c r="BX4" s="38"/>
-      <c r="BY4" s="38"/>
-      <c r="BZ4" s="35"/>
-      <c r="CA4" s="36" t="s">
+      <c r="BT4" s="51"/>
+      <c r="BU4" s="51"/>
+      <c r="BV4" s="51"/>
+      <c r="BW4" s="51"/>
+      <c r="BX4" s="51"/>
+      <c r="BY4" s="51"/>
+      <c r="BZ4" s="49"/>
+      <c r="CA4" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="CB4" s="36" t="s">
+      <c r="CB4" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="CC4" s="36" t="s">
+      <c r="CC4" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="CD4" s="36" t="s">
+      <c r="CD4" s="33" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="1:82">
-      <c r="B5" s="34" t="s">
+    <row r="5" spans="1:82" ht="48" customHeight="1">
+      <c r="B5" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="41" t="s">
+      <c r="K5" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="L5" s="41" t="s">
+      <c r="L5" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="M5" s="41" t="s">
+      <c r="M5" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="N5" s="41" t="s">
+      <c r="N5" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="O5" s="37" t="s">
+      <c r="O5" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="P5" s="37" t="s">
+      <c r="P5" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Q5" s="37" t="s">
+      <c r="Q5" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="R5" s="37" t="s">
+      <c r="R5" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="S5" s="37" t="s">
+      <c r="S5" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="T5" s="37" t="s">
+      <c r="T5" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="U5" s="37" t="s">
+      <c r="U5" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="V5" s="37" t="s">
+      <c r="V5" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="W5" s="37" t="s">
+      <c r="W5" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="X5" s="37" t="s">
+      <c r="X5" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Y5" s="37" t="s">
+      <c r="Y5" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="Z5" s="37" t="s">
+      <c r="Z5" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="AA5" s="37" t="s">
+      <c r="AA5" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="AB5" s="37" t="s">
+      <c r="AB5" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="AC5" s="37" t="s">
+      <c r="AC5" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="AD5" s="37" t="s">
+      <c r="AD5" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="AE5" s="42" t="s">
+      <c r="AE5" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="AF5" s="42" t="s">
+      <c r="AF5" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="AG5" s="42" t="s">
+      <c r="AG5" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="AH5" s="42" t="s">
+      <c r="AH5" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="AI5" s="42" t="s">
+      <c r="AI5" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="AJ5" s="42" t="s">
+      <c r="AJ5" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="AK5" s="42" t="s">
+      <c r="AK5" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="AL5" s="42" t="s">
+      <c r="AL5" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="AM5" s="42" t="s">
+      <c r="AM5" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="AN5" s="42" t="s">
+      <c r="AN5" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="AO5" s="42" t="s">
+      <c r="AO5" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="AP5" s="42" t="s">
+      <c r="AP5" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="AQ5" s="42" t="s">
+      <c r="AQ5" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="AR5" s="42" t="s">
+      <c r="AR5" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="AS5" s="42" t="s">
+      <c r="AS5" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="AT5" s="42" t="s">
+      <c r="AT5" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="AU5" s="42" t="s">
+      <c r="AU5" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="AV5" s="42" t="s">
+      <c r="AV5" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="AW5" s="42" t="s">
+      <c r="AW5" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="AX5" s="42" t="s">
+      <c r="AX5" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="AY5" s="42" t="s">
+      <c r="AY5" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="AZ5" s="42" t="s">
+      <c r="AZ5" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="BA5" s="42" t="s">
+      <c r="BA5" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="BB5" s="42" t="s">
+      <c r="BB5" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="BC5" s="43" t="s">
+      <c r="BC5" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="BD5" s="43" t="s">
+      <c r="BD5" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="BE5" s="43" t="s">
+      <c r="BE5" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="BF5" s="43" t="s">
+      <c r="BF5" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="BG5" s="43" t="s">
+      <c r="BG5" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="BH5" s="43" t="s">
+      <c r="BH5" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="BI5" s="43" t="s">
+      <c r="BI5" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="BJ5" s="43" t="s">
+      <c r="BJ5" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="BK5" s="43" t="s">
+      <c r="BK5" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="BL5" s="43" t="s">
+      <c r="BL5" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="BM5" s="43" t="s">
+      <c r="BM5" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="BN5" s="43" t="s">
+      <c r="BN5" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="BO5" s="43" t="s">
+      <c r="BO5" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="BP5" s="43" t="s">
+      <c r="BP5" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="BQ5" s="43" t="s">
+      <c r="BQ5" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="BR5" s="43" t="s">
+      <c r="BR5" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="BS5" s="43" t="s">
+      <c r="BS5" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="BT5" s="43" t="s">
+      <c r="BT5" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="BU5" s="43" t="s">
+      <c r="BU5" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="BV5" s="43" t="s">
+      <c r="BV5" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="BW5" s="43" t="s">
+      <c r="BW5" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="BX5" s="43" t="s">
+      <c r="BX5" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="BY5" s="43" t="s">
+      <c r="BY5" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="BZ5" s="43" t="s">
+      <c r="BZ5" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="CA5" s="41" t="s">
+      <c r="CA5" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="CB5" s="41" t="s">
+      <c r="CB5" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="CC5" s="41" t="s">
+      <c r="CC5" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="CD5" s="41" t="s">
+      <c r="CD5" s="35" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" s="17" customFormat="1" ht="58.15" spans="1:82">
-      <c r="A6" s="44" t="s">
+    <row r="6" spans="1:82" s="17" customFormat="1" ht="57">
+      <c r="A6" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="I6" s="44" t="s">
+      <c r="I6" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="K6" s="44" t="s">
+      <c r="K6" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="L6" s="44" t="s">
+      <c r="L6" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="M6" s="47" t="s">
+      <c r="M6" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="N6" s="47" t="s">
+      <c r="N6" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="O6" s="44" t="s">
+      <c r="O6" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="P6" s="48" t="s">
+      <c r="P6" s="42" t="s">
         <v>148</v>
       </c>
-      <c r="Q6" s="48" t="s">
+      <c r="Q6" s="42" t="s">
         <v>149</v>
       </c>
-      <c r="R6" s="48" t="s">
+      <c r="R6" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="S6" s="48" t="s">
+      <c r="S6" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="T6" s="48" t="s">
+      <c r="T6" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="U6" s="48" t="s">
+      <c r="U6" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="V6" s="48" t="s">
+      <c r="V6" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="W6" s="48" t="s">
+      <c r="W6" s="42" t="s">
         <v>155</v>
       </c>
-      <c r="X6" s="49" t="s">
+      <c r="X6" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="Y6" s="48" t="s">
+      <c r="Y6" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="Z6" s="48" t="s">
+      <c r="Z6" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="AA6" s="48" t="s">
+      <c r="AA6" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="AB6" s="48" t="s">
+      <c r="AB6" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="AC6" s="49" t="s">
+      <c r="AC6" s="43" t="s">
         <v>161</v>
       </c>
-      <c r="AD6" s="48" t="s">
+      <c r="AD6" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="AE6" s="48" t="s">
+      <c r="AE6" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="AF6" s="48" t="s">
+      <c r="AF6" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="AG6" s="48" t="s">
+      <c r="AG6" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="AH6" s="49" t="s">
+      <c r="AH6" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="AI6" s="48" t="s">
+      <c r="AI6" s="42" t="s">
         <v>167</v>
       </c>
-      <c r="AJ6" s="48" t="s">
+      <c r="AJ6" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="AK6" s="48" t="s">
+      <c r="AK6" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="AL6" s="48" t="s">
+      <c r="AL6" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="AM6" s="49" t="s">
+      <c r="AM6" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="AN6" s="48" t="s">
+      <c r="AN6" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="AO6" s="48" t="s">
+      <c r="AO6" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="AP6" s="48" t="s">
+      <c r="AP6" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="AQ6" s="48" t="s">
+      <c r="AQ6" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="AR6" s="49" t="s">
+      <c r="AR6" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="AS6" s="48" t="s">
+      <c r="AS6" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="AT6" s="48" t="s">
+      <c r="AT6" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="AU6" s="48" t="s">
+      <c r="AU6" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="AV6" s="48" t="s">
+      <c r="AV6" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="AW6" s="49" t="s">
+      <c r="AW6" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="AX6" s="48" t="s">
+      <c r="AX6" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="AY6" s="48" t="s">
+      <c r="AY6" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="AZ6" s="48" t="s">
+      <c r="AZ6" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="BA6" s="48" t="s">
+      <c r="BA6" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="BB6" s="49" t="s">
+      <c r="BB6" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="BC6" s="48" t="s">
+      <c r="BC6" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="BD6" s="48" t="s">
+      <c r="BD6" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="BE6" s="50" t="s">
+      <c r="BE6" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="BF6" s="50" t="s">
+      <c r="BF6" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="BG6" s="50" t="s">
+      <c r="BG6" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="BH6" s="48" t="s">
+      <c r="BH6" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="BI6" s="48" t="s">
+      <c r="BI6" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="BJ6" s="49" t="s">
+      <c r="BJ6" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="BK6" s="47" t="s">
+      <c r="BK6" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="BL6" s="44" t="s">
+      <c r="BL6" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="BM6" s="51" t="s">
+      <c r="BM6" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="BN6" s="51" t="s">
+      <c r="BN6" s="45" t="s">
         <v>198</v>
       </c>
-      <c r="BO6" s="51" t="s">
+      <c r="BO6" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="BP6" s="51" t="s">
+      <c r="BP6" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="BQ6" s="51" t="s">
+      <c r="BQ6" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="BR6" s="51" t="s">
+      <c r="BR6" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="BS6" s="51" t="s">
+      <c r="BS6" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="BT6" s="51" t="s">
+      <c r="BT6" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="BU6" s="51" t="s">
+      <c r="BU6" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="BV6" s="51" t="s">
+      <c r="BV6" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="BW6" s="51" t="s">
+      <c r="BW6" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="BX6" s="51" t="s">
+      <c r="BX6" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="BY6" s="51" t="s">
+      <c r="BY6" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="BZ6" s="51" t="s">
+      <c r="BZ6" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="CA6" s="51" t="s">
+      <c r="CA6" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="CB6" s="51" t="s">
+      <c r="CB6" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="CC6" s="51" t="s">
+      <c r="CC6" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="CD6" s="51" t="s">
+      <c r="CD6" s="45" t="s">
         <v>214</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AM4:AT4"/>
+    <mergeCell ref="AU4:BB4"/>
+    <mergeCell ref="BC4:BJ4"/>
+    <mergeCell ref="BK4:BR4"/>
+    <mergeCell ref="BS4:BZ4"/>
     <mergeCell ref="E2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="O4:V4"/>
     <mergeCell ref="W4:AD4"/>
     <mergeCell ref="AE4:AL4"/>
-    <mergeCell ref="AM4:AT4"/>
-    <mergeCell ref="AU4:BB4"/>
-    <mergeCell ref="BC4:BJ4"/>
-    <mergeCell ref="BK4:BR4"/>
-    <mergeCell ref="BS4:BZ4"/>
   </mergeCells>
+  <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="G3:H3">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5 AA5 AI5 AQ5 AY5 BG5 BO5 BW5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5 AA5 AI5 AQ5 AY5 BG5 BO5 BW5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.6" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
   <cols>
     <col min="1" max="1" width="3" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="3" customWidth="1"/>
-    <col min="3" max="4" width="5.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="34.125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="34.125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="5" customWidth="1"/>
-    <col min="11" max="11" width="5.75" style="5" customWidth="1"/>
-    <col min="12" max="14" width="5.75" style="4" customWidth="1"/>
-    <col min="15" max="15" width="27.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.8984375" style="3" customWidth="1"/>
+    <col min="3" max="4" width="5.59765625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.69921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.19921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.09765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="34.09765625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.69921875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="5.69921875" style="5" customWidth="1"/>
+    <col min="12" max="14" width="5.69921875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="27.3984375" style="4" customWidth="1"/>
     <col min="16" max="16" width="9" style="4" customWidth="1"/>
     <col min="17" max="17" width="8" style="4" customWidth="1"/>
     <col min="18" max="16384" width="8" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1" spans="1:16">
+    <row r="1" spans="1:16" hidden="1">
       <c r="A1" s="2" t="s">
         <v>215</v>
       </c>
@@ -3843,7 +3251,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" ht="33.75" customHeight="1" spans="1:16">
+    <row r="2" spans="1:16" ht="33.75" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -3863,7 +3271,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="34.15" customHeight="1" spans="1:16">
+    <row r="3" spans="1:16" s="1" customFormat="1" ht="34.200000000000003" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>232</v>
       </c>
@@ -3913,7 +3321,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:16">
+    <row r="4" spans="1:16" s="1" customFormat="1" ht="68.25" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>245</v>
       </c>
@@ -3963,7 +3371,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" ht="11.45" customHeight="1" spans="1:16">
+    <row r="5" spans="1:16" ht="11.4" customHeight="1">
       <c r="A5" s="13" t="s">
         <v>259</v>
       </c>
@@ -4009,17 +3417,15 @@
       <c r="O5" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P5" s="6" t="s">
         <v>214</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P5" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A4:P5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EB800A-B409-4D29-BB0F-D7A3FB210511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD6541D-E713-44EA-A4F9-B33A631A864C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="1" r:id="rId1"/>
@@ -300,6 +300,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>全钢硫化工程生产计划单</t>
@@ -492,6 +493,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>版本号</t>
@@ -510,6 +512,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：</t>
@@ -530,6 +533,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>班产合计</t>
@@ -549,6 +553,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：</t>
@@ -1150,12 +1155,12 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="m/d;@"/>
-    <numFmt numFmtId="180" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="181" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="182" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="183" formatCode="[$-10804]0;\(0\)"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="m/d;@"/>
+    <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="179" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1166,22 +1171,26 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1194,6 +1203,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1218,6 +1228,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1231,6 +1242,7 @@
       <b/>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1242,6 +1254,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1249,6 +1262,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1259,6 +1273,7 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1266,6 +1281,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1273,17 +1289,20 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1421,15 +1440,15 @@
   </borders>
   <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="180" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1437,16 +1456,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="18" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
@@ -1455,25 +1474,25 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1488,7 +1507,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1512,28 +1531,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1569,17 +1588,25 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1588,16 +1615,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2039,39 +2061,39 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CD6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="4.8984375" customWidth="1"/>
-    <col min="2" max="4" width="5.59765625" customWidth="1"/>
+    <col min="1" max="1" width="4.875" customWidth="1"/>
+    <col min="2" max="4" width="5.625" customWidth="1"/>
     <col min="5" max="5" width="6.5" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" customWidth="1"/>
-    <col min="7" max="7" width="32.59765625" customWidth="1"/>
+    <col min="6" max="6" width="9.625" customWidth="1"/>
+    <col min="7" max="7" width="32.625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="17.09765625" customWidth="1"/>
-    <col min="11" max="12" width="5.59765625" customWidth="1"/>
-    <col min="13" max="13" width="6.09765625" customWidth="1"/>
-    <col min="14" max="14" width="5.59765625" customWidth="1"/>
-    <col min="15" max="15" width="3.09765625" customWidth="1"/>
-    <col min="16" max="22" width="5.09765625" customWidth="1"/>
-    <col min="23" max="23" width="3.09765625" customWidth="1"/>
-    <col min="24" max="30" width="5.09765625" customWidth="1"/>
-    <col min="31" max="31" width="3.09765625" customWidth="1"/>
-    <col min="32" max="38" width="5.09765625" customWidth="1"/>
-    <col min="39" max="39" width="3.09765625" customWidth="1"/>
-    <col min="40" max="46" width="5.09765625" customWidth="1"/>
-    <col min="47" max="47" width="3.09765625" customWidth="1"/>
-    <col min="48" max="54" width="5.09765625" customWidth="1"/>
-    <col min="55" max="55" width="3.09765625" customWidth="1"/>
-    <col min="56" max="62" width="5.09765625" customWidth="1"/>
-    <col min="63" max="63" width="3.09765625" customWidth="1"/>
-    <col min="64" max="70" width="5.09765625" customWidth="1"/>
-    <col min="71" max="71" width="3.09765625" customWidth="1"/>
-    <col min="72" max="78" width="5.09765625" customWidth="1"/>
-    <col min="79" max="79" width="9.59765625" customWidth="1"/>
-    <col min="80" max="80" width="7.59765625" customWidth="1"/>
-    <col min="81" max="81" width="9.59765625" customWidth="1"/>
-    <col min="82" max="82" width="37.59765625" style="18" customWidth="1"/>
+    <col min="10" max="10" width="17.125" customWidth="1"/>
+    <col min="11" max="12" width="5.625" customWidth="1"/>
+    <col min="13" max="13" width="6.125" customWidth="1"/>
+    <col min="14" max="14" width="5.625" customWidth="1"/>
+    <col min="15" max="15" width="3.125" customWidth="1"/>
+    <col min="16" max="22" width="5.125" customWidth="1"/>
+    <col min="23" max="23" width="3.125" customWidth="1"/>
+    <col min="24" max="30" width="5.125" customWidth="1"/>
+    <col min="31" max="31" width="3.125" customWidth="1"/>
+    <col min="32" max="38" width="5.125" customWidth="1"/>
+    <col min="39" max="39" width="3.125" customWidth="1"/>
+    <col min="40" max="46" width="5.125" customWidth="1"/>
+    <col min="47" max="47" width="3.125" customWidth="1"/>
+    <col min="48" max="54" width="5.125" customWidth="1"/>
+    <col min="55" max="55" width="3.125" customWidth="1"/>
+    <col min="56" max="62" width="5.125" customWidth="1"/>
+    <col min="63" max="63" width="3.125" customWidth="1"/>
+    <col min="64" max="70" width="5.125" customWidth="1"/>
+    <col min="71" max="71" width="3.125" customWidth="1"/>
+    <col min="72" max="78" width="5.125" customWidth="1"/>
+    <col min="79" max="79" width="9.625" customWidth="1"/>
+    <col min="80" max="80" width="7.625" customWidth="1"/>
+    <col min="81" max="81" width="9.625" customWidth="1"/>
+    <col min="82" max="82" width="37.625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:82" hidden="1">
@@ -2326,13 +2348,13 @@
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
       <c r="J2" s="17"/>
       <c r="K2" s="20" t="s">
         <v>83</v>
@@ -2409,7 +2431,7 @@
       <c r="CC2" s="21"/>
       <c r="CD2" s="22"/>
     </row>
-    <row r="3" spans="1:82" ht="16.95" customHeight="1">
+    <row r="3" spans="1:82" ht="16.899999999999999" customHeight="1">
       <c r="B3" s="23">
         <f>SUM(B6:B108139)</f>
         <v>0</v>
@@ -2525,10 +2547,10 @@
       <c r="CD3" s="31"/>
     </row>
     <row r="4" spans="1:82" ht="36" customHeight="1">
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="49"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="33" t="s">
         <v>86</v>
       </c>
@@ -2562,86 +2584,86 @@
       <c r="N4" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="50" t="s">
+      <c r="O4" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="49"/>
-      <c r="W4" s="50" t="s">
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="49"/>
-      <c r="AE4" s="52" t="s">
+      <c r="X4" s="47"/>
+      <c r="Y4" s="47"/>
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="47"/>
+      <c r="AB4" s="47"/>
+      <c r="AC4" s="47"/>
+      <c r="AD4" s="48"/>
+      <c r="AE4" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="51"/>
-      <c r="AH4" s="51"/>
-      <c r="AI4" s="51"/>
-      <c r="AJ4" s="51"/>
-      <c r="AK4" s="51"/>
-      <c r="AL4" s="49"/>
-      <c r="AM4" s="52" t="s">
+      <c r="AF4" s="47"/>
+      <c r="AG4" s="47"/>
+      <c r="AH4" s="47"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47"/>
+      <c r="AK4" s="47"/>
+      <c r="AL4" s="48"/>
+      <c r="AM4" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="AN4" s="51"/>
-      <c r="AO4" s="51"/>
-      <c r="AP4" s="51"/>
-      <c r="AQ4" s="51"/>
-      <c r="AR4" s="51"/>
-      <c r="AS4" s="51"/>
-      <c r="AT4" s="49"/>
-      <c r="AU4" s="52" t="s">
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="47"/>
+      <c r="AP4" s="47"/>
+      <c r="AQ4" s="47"/>
+      <c r="AR4" s="47"/>
+      <c r="AS4" s="47"/>
+      <c r="AT4" s="48"/>
+      <c r="AU4" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="AV4" s="51"/>
-      <c r="AW4" s="51"/>
-      <c r="AX4" s="51"/>
-      <c r="AY4" s="51"/>
-      <c r="AZ4" s="51"/>
-      <c r="BA4" s="51"/>
-      <c r="BB4" s="49"/>
-      <c r="BC4" s="53" t="s">
+      <c r="AV4" s="47"/>
+      <c r="AW4" s="47"/>
+      <c r="AX4" s="47"/>
+      <c r="AY4" s="47"/>
+      <c r="AZ4" s="47"/>
+      <c r="BA4" s="47"/>
+      <c r="BB4" s="48"/>
+      <c r="BC4" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="BD4" s="51"/>
-      <c r="BE4" s="51"/>
-      <c r="BF4" s="51"/>
-      <c r="BG4" s="51"/>
-      <c r="BH4" s="51"/>
-      <c r="BI4" s="51"/>
-      <c r="BJ4" s="49"/>
-      <c r="BK4" s="53" t="s">
+      <c r="BD4" s="47"/>
+      <c r="BE4" s="47"/>
+      <c r="BF4" s="47"/>
+      <c r="BG4" s="47"/>
+      <c r="BH4" s="47"/>
+      <c r="BI4" s="47"/>
+      <c r="BJ4" s="48"/>
+      <c r="BK4" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="BL4" s="51"/>
-      <c r="BM4" s="51"/>
-      <c r="BN4" s="51"/>
-      <c r="BO4" s="51"/>
-      <c r="BP4" s="51"/>
-      <c r="BQ4" s="51"/>
-      <c r="BR4" s="49"/>
-      <c r="BS4" s="53" t="s">
+      <c r="BL4" s="47"/>
+      <c r="BM4" s="47"/>
+      <c r="BN4" s="47"/>
+      <c r="BO4" s="47"/>
+      <c r="BP4" s="47"/>
+      <c r="BQ4" s="47"/>
+      <c r="BR4" s="48"/>
+      <c r="BS4" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="BT4" s="51"/>
-      <c r="BU4" s="51"/>
-      <c r="BV4" s="51"/>
-      <c r="BW4" s="51"/>
-      <c r="BX4" s="51"/>
-      <c r="BY4" s="51"/>
-      <c r="BZ4" s="49"/>
+      <c r="BT4" s="47"/>
+      <c r="BU4" s="47"/>
+      <c r="BV4" s="47"/>
+      <c r="BW4" s="47"/>
+      <c r="BX4" s="47"/>
+      <c r="BY4" s="47"/>
+      <c r="BZ4" s="48"/>
       <c r="CA4" s="33" t="s">
         <v>105</v>
       </c>
@@ -2900,7 +2922,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:82" s="17" customFormat="1" ht="57">
+    <row r="6" spans="1:82" s="17" customFormat="1" ht="60">
       <c r="A6" s="38" t="s">
         <v>133</v>
       </c>
@@ -3150,16 +3172,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="AE4:AL4"/>
     <mergeCell ref="AM4:AT4"/>
     <mergeCell ref="AU4:BB4"/>
     <mergeCell ref="BC4:BJ4"/>
     <mergeCell ref="BK4:BR4"/>
     <mergeCell ref="BS4:BZ4"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="AE4:AL4"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="G3:H3">
@@ -3182,20 +3204,20 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="3" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.8984375" style="3" customWidth="1"/>
-    <col min="3" max="4" width="5.59765625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="4.69921875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="34.09765625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="34.09765625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.69921875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="5.69921875" style="5" customWidth="1"/>
-    <col min="12" max="14" width="5.69921875" style="4" customWidth="1"/>
-    <col min="15" max="15" width="27.3984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="3" customWidth="1"/>
+    <col min="3" max="4" width="5.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="34.125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="5" customWidth="1"/>
+    <col min="11" max="11" width="5.75" style="5" customWidth="1"/>
+    <col min="12" max="14" width="5.75" style="4" customWidth="1"/>
+    <col min="15" max="15" width="27.375" style="4" customWidth="1"/>
     <col min="16" max="16" width="9" style="4" customWidth="1"/>
     <col min="17" max="17" width="8" style="4" customWidth="1"/>
     <col min="18" max="16384" width="8" style="4"/>
@@ -3271,7 +3293,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="3" spans="1:16" s="1" customFormat="1" ht="34.15" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>232</v>
       </c>
@@ -3371,7 +3393,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="11.4" customHeight="1">
+    <row r="5" spans="1:16" ht="11.45" customHeight="1">
       <c r="A5" s="13" t="s">
         <v>259</v>
       </c>
@@ -3399,7 +3421,7 @@
       <c r="I5" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="54" t="s">
         <v>267</v>
       </c>
       <c r="K5" s="16" t="s">

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD6541D-E713-44EA-A4F9-B33A631A864C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B2F3AD-1728-4B55-AB15-10D7E4CB2D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="1" r:id="rId1"/>
@@ -1600,13 +1600,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1615,11 +1610,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2061,39 +2061,39 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CD6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="4.875" customWidth="1"/>
-    <col min="2" max="4" width="5.625" customWidth="1"/>
+    <col min="1" max="1" width="4.8984375" customWidth="1"/>
+    <col min="2" max="4" width="5.59765625" customWidth="1"/>
     <col min="5" max="5" width="6.5" customWidth="1"/>
-    <col min="6" max="6" width="9.625" customWidth="1"/>
-    <col min="7" max="7" width="32.625" customWidth="1"/>
+    <col min="6" max="6" width="9.59765625" customWidth="1"/>
+    <col min="7" max="7" width="32.59765625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="12" width="5.625" customWidth="1"/>
-    <col min="13" max="13" width="6.125" customWidth="1"/>
-    <col min="14" max="14" width="5.625" customWidth="1"/>
-    <col min="15" max="15" width="3.125" customWidth="1"/>
-    <col min="16" max="22" width="5.125" customWidth="1"/>
-    <col min="23" max="23" width="3.125" customWidth="1"/>
-    <col min="24" max="30" width="5.125" customWidth="1"/>
-    <col min="31" max="31" width="3.125" customWidth="1"/>
-    <col min="32" max="38" width="5.125" customWidth="1"/>
-    <col min="39" max="39" width="3.125" customWidth="1"/>
-    <col min="40" max="46" width="5.125" customWidth="1"/>
-    <col min="47" max="47" width="3.125" customWidth="1"/>
-    <col min="48" max="54" width="5.125" customWidth="1"/>
-    <col min="55" max="55" width="3.125" customWidth="1"/>
-    <col min="56" max="62" width="5.125" customWidth="1"/>
-    <col min="63" max="63" width="3.125" customWidth="1"/>
-    <col min="64" max="70" width="5.125" customWidth="1"/>
-    <col min="71" max="71" width="3.125" customWidth="1"/>
-    <col min="72" max="78" width="5.125" customWidth="1"/>
-    <col min="79" max="79" width="9.625" customWidth="1"/>
-    <col min="80" max="80" width="7.625" customWidth="1"/>
-    <col min="81" max="81" width="9.625" customWidth="1"/>
-    <col min="82" max="82" width="37.625" style="18" customWidth="1"/>
+    <col min="10" max="10" width="17.09765625" customWidth="1"/>
+    <col min="11" max="12" width="5.59765625" customWidth="1"/>
+    <col min="13" max="13" width="6.09765625" customWidth="1"/>
+    <col min="14" max="14" width="5.59765625" customWidth="1"/>
+    <col min="15" max="15" width="3.09765625" customWidth="1"/>
+    <col min="16" max="22" width="5.09765625" customWidth="1"/>
+    <col min="23" max="23" width="3.09765625" customWidth="1"/>
+    <col min="24" max="30" width="5.09765625" customWidth="1"/>
+    <col min="31" max="31" width="3.09765625" customWidth="1"/>
+    <col min="32" max="38" width="5.09765625" customWidth="1"/>
+    <col min="39" max="39" width="3.09765625" customWidth="1"/>
+    <col min="40" max="46" width="5.09765625" customWidth="1"/>
+    <col min="47" max="47" width="3.09765625" customWidth="1"/>
+    <col min="48" max="54" width="5.09765625" customWidth="1"/>
+    <col min="55" max="55" width="3.09765625" customWidth="1"/>
+    <col min="56" max="62" width="5.09765625" customWidth="1"/>
+    <col min="63" max="63" width="3.09765625" customWidth="1"/>
+    <col min="64" max="70" width="5.09765625" customWidth="1"/>
+    <col min="71" max="71" width="3.09765625" customWidth="1"/>
+    <col min="72" max="78" width="5.09765625" customWidth="1"/>
+    <col min="79" max="79" width="9.59765625" customWidth="1"/>
+    <col min="80" max="80" width="7.59765625" customWidth="1"/>
+    <col min="81" max="81" width="9.59765625" customWidth="1"/>
+    <col min="82" max="82" width="37.59765625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:82" hidden="1">
@@ -2348,13 +2348,13 @@
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="17"/>
       <c r="K2" s="20" t="s">
         <v>83</v>
@@ -2431,7 +2431,7 @@
       <c r="CC2" s="21"/>
       <c r="CD2" s="22"/>
     </row>
-    <row r="3" spans="1:82" ht="16.899999999999999" customHeight="1">
+    <row r="3" spans="1:82" ht="16.95" customHeight="1">
       <c r="B3" s="23">
         <f>SUM(B6:B108139)</f>
         <v>0</v>
@@ -2547,10 +2547,10 @@
       <c r="CD3" s="31"/>
     </row>
     <row r="4" spans="1:82" ht="36" customHeight="1">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="48"/>
+      <c r="C4" s="50"/>
       <c r="D4" s="33" t="s">
         <v>86</v>
       </c>
@@ -2584,86 +2584,86 @@
       <c r="N4" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="53" t="s">
+      <c r="O4" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="48"/>
-      <c r="W4" s="53" t="s">
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="50"/>
+      <c r="W4" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="X4" s="47"/>
-      <c r="Y4" s="47"/>
-      <c r="Z4" s="47"/>
-      <c r="AA4" s="47"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="47"/>
-      <c r="AD4" s="48"/>
-      <c r="AE4" s="46" t="s">
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="50"/>
+      <c r="AE4" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="AF4" s="47"/>
-      <c r="AG4" s="47"/>
-      <c r="AH4" s="47"/>
-      <c r="AI4" s="47"/>
-      <c r="AJ4" s="47"/>
-      <c r="AK4" s="47"/>
-      <c r="AL4" s="48"/>
-      <c r="AM4" s="46" t="s">
+      <c r="AF4" s="52"/>
+      <c r="AG4" s="52"/>
+      <c r="AH4" s="52"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="52"/>
+      <c r="AK4" s="52"/>
+      <c r="AL4" s="50"/>
+      <c r="AM4" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="AN4" s="47"/>
-      <c r="AO4" s="47"/>
-      <c r="AP4" s="47"/>
-      <c r="AQ4" s="47"/>
-      <c r="AR4" s="47"/>
-      <c r="AS4" s="47"/>
-      <c r="AT4" s="48"/>
-      <c r="AU4" s="46" t="s">
+      <c r="AN4" s="52"/>
+      <c r="AO4" s="52"/>
+      <c r="AP4" s="52"/>
+      <c r="AQ4" s="52"/>
+      <c r="AR4" s="52"/>
+      <c r="AS4" s="52"/>
+      <c r="AT4" s="50"/>
+      <c r="AU4" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="AV4" s="47"/>
-      <c r="AW4" s="47"/>
-      <c r="AX4" s="47"/>
-      <c r="AY4" s="47"/>
-      <c r="AZ4" s="47"/>
-      <c r="BA4" s="47"/>
-      <c r="BB4" s="48"/>
-      <c r="BC4" s="49" t="s">
+      <c r="AV4" s="52"/>
+      <c r="AW4" s="52"/>
+      <c r="AX4" s="52"/>
+      <c r="AY4" s="52"/>
+      <c r="AZ4" s="52"/>
+      <c r="BA4" s="52"/>
+      <c r="BB4" s="50"/>
+      <c r="BC4" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="BD4" s="47"/>
-      <c r="BE4" s="47"/>
-      <c r="BF4" s="47"/>
-      <c r="BG4" s="47"/>
-      <c r="BH4" s="47"/>
-      <c r="BI4" s="47"/>
-      <c r="BJ4" s="48"/>
-      <c r="BK4" s="49" t="s">
+      <c r="BD4" s="52"/>
+      <c r="BE4" s="52"/>
+      <c r="BF4" s="52"/>
+      <c r="BG4" s="52"/>
+      <c r="BH4" s="52"/>
+      <c r="BI4" s="52"/>
+      <c r="BJ4" s="50"/>
+      <c r="BK4" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="BL4" s="47"/>
-      <c r="BM4" s="47"/>
-      <c r="BN4" s="47"/>
-      <c r="BO4" s="47"/>
-      <c r="BP4" s="47"/>
-      <c r="BQ4" s="47"/>
-      <c r="BR4" s="48"/>
-      <c r="BS4" s="49" t="s">
+      <c r="BL4" s="52"/>
+      <c r="BM4" s="52"/>
+      <c r="BN4" s="52"/>
+      <c r="BO4" s="52"/>
+      <c r="BP4" s="52"/>
+      <c r="BQ4" s="52"/>
+      <c r="BR4" s="50"/>
+      <c r="BS4" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="BT4" s="47"/>
-      <c r="BU4" s="47"/>
-      <c r="BV4" s="47"/>
-      <c r="BW4" s="47"/>
-      <c r="BX4" s="47"/>
-      <c r="BY4" s="47"/>
-      <c r="BZ4" s="48"/>
+      <c r="BT4" s="52"/>
+      <c r="BU4" s="52"/>
+      <c r="BV4" s="52"/>
+      <c r="BW4" s="52"/>
+      <c r="BX4" s="52"/>
+      <c r="BY4" s="52"/>
+      <c r="BZ4" s="50"/>
       <c r="CA4" s="33" t="s">
         <v>105</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:82" s="17" customFormat="1" ht="60">
+    <row r="6" spans="1:82" s="17" customFormat="1" ht="57">
       <c r="A6" s="38" t="s">
         <v>133</v>
       </c>
@@ -3172,16 +3172,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AM4:AT4"/>
+    <mergeCell ref="AU4:BB4"/>
+    <mergeCell ref="BC4:BJ4"/>
+    <mergeCell ref="BK4:BR4"/>
+    <mergeCell ref="BS4:BZ4"/>
     <mergeCell ref="E2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="O4:V4"/>
     <mergeCell ref="W4:AD4"/>
     <mergeCell ref="AE4:AL4"/>
-    <mergeCell ref="AM4:AT4"/>
-    <mergeCell ref="AU4:BB4"/>
-    <mergeCell ref="BC4:BJ4"/>
-    <mergeCell ref="BK4:BR4"/>
-    <mergeCell ref="BS4:BZ4"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="G3:H3">
@@ -3204,20 +3204,20 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
   <cols>
     <col min="1" max="1" width="3" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="3" customWidth="1"/>
-    <col min="3" max="4" width="5.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="34.125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="34.125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="5" customWidth="1"/>
-    <col min="11" max="11" width="5.75" style="5" customWidth="1"/>
-    <col min="12" max="14" width="5.75" style="4" customWidth="1"/>
-    <col min="15" max="15" width="27.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.8984375" style="3" customWidth="1"/>
+    <col min="3" max="4" width="5.59765625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.69921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.19921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.09765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="34.09765625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.69921875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="5.69921875" style="5" customWidth="1"/>
+    <col min="12" max="14" width="5.69921875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="27.3984375" style="4" customWidth="1"/>
     <col min="16" max="16" width="9" style="4" customWidth="1"/>
     <col min="17" max="17" width="8" style="4" customWidth="1"/>
     <col min="18" max="16384" width="8" style="4"/>
@@ -3293,7 +3293,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="34.15" customHeight="1">
+    <row r="3" spans="1:16" s="1" customFormat="1" ht="34.200000000000003" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>232</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="11.45" customHeight="1">
+    <row r="5" spans="1:16" ht="11.4" customHeight="1">
       <c r="A5" s="13" t="s">
         <v>259</v>
       </c>
@@ -3421,7 +3421,7 @@
       <c r="I5" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="J5" s="46" t="s">
         <v>267</v>
       </c>
       <c r="K5" s="16" t="s">
@@ -3439,7 +3439,7 @@
       <c r="O5" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="13" t="s">
         <v>214</v>
       </c>
     </row>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B2F3AD-1728-4B55-AB15-10D7E4CB2D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0F0F5B-D877-46BA-8028-066ED92B5EBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$4:$P$5</definedName>
     <definedName name="A">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="12"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1162,7 +1162,7 @@
     <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1463,7 +1463,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1620,6 +1620,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2060,43 +2066,43 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:CD6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+  <dimension ref="A1:CD47"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.8984375" customWidth="1"/>
-    <col min="2" max="4" width="5.59765625" customWidth="1"/>
+    <col min="1" max="1" width="4.875" customWidth="1"/>
+    <col min="2" max="4" width="5.625" customWidth="1"/>
     <col min="5" max="5" width="6.5" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" customWidth="1"/>
-    <col min="7" max="7" width="32.59765625" customWidth="1"/>
+    <col min="6" max="6" width="9.625" customWidth="1"/>
+    <col min="7" max="7" width="37.5" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="17.09765625" customWidth="1"/>
-    <col min="11" max="12" width="5.59765625" customWidth="1"/>
-    <col min="13" max="13" width="6.09765625" customWidth="1"/>
-    <col min="14" max="14" width="5.59765625" customWidth="1"/>
-    <col min="15" max="15" width="3.09765625" customWidth="1"/>
-    <col min="16" max="22" width="5.09765625" customWidth="1"/>
-    <col min="23" max="23" width="3.09765625" customWidth="1"/>
-    <col min="24" max="30" width="5.09765625" customWidth="1"/>
-    <col min="31" max="31" width="3.09765625" customWidth="1"/>
-    <col min="32" max="38" width="5.09765625" customWidth="1"/>
-    <col min="39" max="39" width="3.09765625" customWidth="1"/>
-    <col min="40" max="46" width="5.09765625" customWidth="1"/>
-    <col min="47" max="47" width="3.09765625" customWidth="1"/>
-    <col min="48" max="54" width="5.09765625" customWidth="1"/>
-    <col min="55" max="55" width="3.09765625" customWidth="1"/>
-    <col min="56" max="62" width="5.09765625" customWidth="1"/>
-    <col min="63" max="63" width="3.09765625" customWidth="1"/>
-    <col min="64" max="70" width="5.09765625" customWidth="1"/>
-    <col min="71" max="71" width="3.09765625" customWidth="1"/>
-    <col min="72" max="78" width="5.09765625" customWidth="1"/>
-    <col min="79" max="79" width="9.59765625" customWidth="1"/>
-    <col min="80" max="80" width="7.59765625" customWidth="1"/>
-    <col min="81" max="81" width="9.59765625" customWidth="1"/>
-    <col min="82" max="82" width="37.59765625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="32.25" customWidth="1"/>
+    <col min="10" max="10" width="17.125" customWidth="1"/>
+    <col min="11" max="12" width="5.625" customWidth="1"/>
+    <col min="13" max="13" width="6.125" customWidth="1"/>
+    <col min="14" max="14" width="5.625" customWidth="1"/>
+    <col min="15" max="15" width="3.125" customWidth="1"/>
+    <col min="16" max="22" width="5.125" customWidth="1"/>
+    <col min="23" max="23" width="3.125" customWidth="1"/>
+    <col min="24" max="30" width="5.125" customWidth="1"/>
+    <col min="31" max="31" width="3.125" customWidth="1"/>
+    <col min="32" max="38" width="5.125" customWidth="1"/>
+    <col min="39" max="39" width="3.125" customWidth="1"/>
+    <col min="40" max="46" width="5.125" customWidth="1"/>
+    <col min="47" max="47" width="3.125" customWidth="1"/>
+    <col min="48" max="54" width="5.125" customWidth="1"/>
+    <col min="55" max="55" width="3.125" customWidth="1"/>
+    <col min="56" max="62" width="5.125" customWidth="1"/>
+    <col min="63" max="63" width="3.125" customWidth="1"/>
+    <col min="64" max="70" width="5.125" customWidth="1"/>
+    <col min="71" max="71" width="3.125" customWidth="1"/>
+    <col min="72" max="78" width="5.125" customWidth="1"/>
+    <col min="79" max="79" width="9.625" customWidth="1"/>
+    <col min="80" max="80" width="7.625" customWidth="1"/>
+    <col min="81" max="81" width="9.625" customWidth="1"/>
+    <col min="82" max="82" width="37.625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" hidden="1">
+    <row r="1" spans="1:82" hidden="1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2344,7 +2350,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:82" ht="37.5" customHeight="1">
+    <row r="2" spans="1:82" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
@@ -2431,7 +2437,7 @@
       <c r="CC2" s="21"/>
       <c r="CD2" s="22"/>
     </row>
-    <row r="3" spans="1:82" ht="16.95" customHeight="1">
+    <row r="3" spans="1:82" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="23">
         <f>SUM(B6:B108139)</f>
         <v>0</v>
@@ -2546,7 +2552,7 @@
       <c r="CC3" s="24"/>
       <c r="CD3" s="31"/>
     </row>
-    <row r="4" spans="1:82" ht="36" customHeight="1">
+    <row r="4" spans="1:82" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="49" t="s">
         <v>85</v>
       </c>
@@ -2677,7 +2683,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:82" ht="48" customHeight="1">
+    <row r="5" spans="1:82" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="32" t="s">
         <v>109</v>
       </c>
@@ -2922,7 +2928,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:82" s="17" customFormat="1" ht="57">
+    <row r="6" spans="1:82" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.15">
       <c r="A6" s="38" t="s">
         <v>133</v>
       </c>
@@ -2941,13 +2947,13 @@
       <c r="F6" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="56" t="s">
         <v>139</v>
       </c>
       <c r="H6" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="56" t="s">
         <v>141</v>
       </c>
       <c r="J6" s="40" t="s">
@@ -3169,6 +3175,129 @@
       <c r="CD6" s="45" t="s">
         <v>214</v>
       </c>
+    </row>
+    <row r="7" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G7" s="55"/>
+    </row>
+    <row r="8" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G8" s="55"/>
+    </row>
+    <row r="9" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G9" s="55"/>
+    </row>
+    <row r="10" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G10" s="55"/>
+    </row>
+    <row r="11" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G11" s="55"/>
+    </row>
+    <row r="12" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G12" s="55"/>
+    </row>
+    <row r="13" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G13" s="55"/>
+    </row>
+    <row r="14" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G14" s="55"/>
+    </row>
+    <row r="15" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G15" s="55"/>
+    </row>
+    <row r="16" spans="1:82" x14ac:dyDescent="0.15">
+      <c r="G16" s="55"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G17" s="55"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G18" s="55"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G19" s="55"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G20" s="55"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G21" s="55"/>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G22" s="55"/>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G23" s="55"/>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G24" s="55"/>
+    </row>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G25" s="55"/>
+    </row>
+    <row r="26" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G26" s="55"/>
+    </row>
+    <row r="27" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G27" s="55"/>
+    </row>
+    <row r="28" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G28" s="55"/>
+    </row>
+    <row r="29" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G29" s="55"/>
+    </row>
+    <row r="30" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G30" s="55"/>
+    </row>
+    <row r="31" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G31" s="55"/>
+    </row>
+    <row r="32" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G32" s="55"/>
+    </row>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G33" s="55"/>
+    </row>
+    <row r="34" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G34" s="55"/>
+    </row>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G35" s="55"/>
+    </row>
+    <row r="36" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G36" s="55"/>
+    </row>
+    <row r="37" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G37" s="55"/>
+    </row>
+    <row r="38" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G38" s="55"/>
+    </row>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G39" s="55"/>
+    </row>
+    <row r="40" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G40" s="55"/>
+    </row>
+    <row r="41" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G41" s="55"/>
+    </row>
+    <row r="42" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G42" s="55"/>
+    </row>
+    <row r="43" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G43" s="55"/>
+    </row>
+    <row r="44" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G44" s="55"/>
+    </row>
+    <row r="45" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G45" s="55"/>
+    </row>
+    <row r="46" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G46" s="55"/>
+    </row>
+    <row r="47" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G47" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3204,26 +3333,25 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.8984375" style="3" customWidth="1"/>
-    <col min="3" max="4" width="5.59765625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="4.69921875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="34.09765625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="34.09765625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.69921875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="5.69921875" style="5" customWidth="1"/>
-    <col min="12" max="14" width="5.69921875" style="4" customWidth="1"/>
-    <col min="15" max="15" width="27.3984375" style="4" customWidth="1"/>
-    <col min="16" max="16" width="9" style="4" customWidth="1"/>
+    <col min="1" max="1" width="4.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="3" customWidth="1"/>
+    <col min="3" max="4" width="5.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="5.25" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="34.125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="5" customWidth="1"/>
+    <col min="11" max="11" width="6.75" style="5" customWidth="1"/>
+    <col min="12" max="14" width="6.75" style="4" customWidth="1"/>
+    <col min="15" max="16" width="27.375" style="4" customWidth="1"/>
     <col min="17" max="17" width="8" style="4" customWidth="1"/>
     <col min="18" max="16384" width="8" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" hidden="1">
+    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>215</v>
       </c>
@@ -3273,7 +3401,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="33.75" customHeight="1">
+    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -3293,7 +3421,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="3" spans="1:16" s="1" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="11" t="s">
         <v>232</v>
       </c>
@@ -3343,7 +3471,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" ht="68.25" customHeight="1">
+    <row r="4" spans="1:16" s="1" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12" t="s">
         <v>245</v>
       </c>
@@ -3393,7 +3521,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="11.4" customHeight="1">
+    <row r="5" spans="1:16" ht="11.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
         <v>259</v>
       </c>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0F0F5B-D877-46BA-8028-066ED92B5EBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB232DE-7D8A-4F2F-843B-3A342800504F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1603,6 +1603,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1610,22 +1624,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2074,7 +2074,7 @@
     <col min="5" max="5" width="6.5" customWidth="1"/>
     <col min="6" max="6" width="9.625" customWidth="1"/>
     <col min="7" max="7" width="37.5" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="8" max="8" width="14.625" customWidth="1"/>
     <col min="9" max="9" width="32.25" customWidth="1"/>
     <col min="10" max="10" width="17.125" customWidth="1"/>
     <col min="11" max="12" width="5.625" customWidth="1"/>
@@ -2354,13 +2354,13 @@
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
       <c r="J2" s="17"/>
       <c r="K2" s="20" t="s">
         <v>83</v>
@@ -2553,10 +2553,10 @@
       <c r="CD3" s="31"/>
     </row>
     <row r="4" spans="1:82" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="50"/>
+      <c r="C4" s="51"/>
       <c r="D4" s="33" t="s">
         <v>86</v>
       </c>
@@ -2590,86 +2590,86 @@
       <c r="N4" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="51" t="s">
+      <c r="O4" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="51" t="s">
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="50"/>
+      <c r="V4" s="51"/>
+      <c r="W4" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="52"/>
-      <c r="AB4" s="52"/>
-      <c r="AC4" s="52"/>
-      <c r="AD4" s="50"/>
-      <c r="AE4" s="53" t="s">
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
+      <c r="Z4" s="50"/>
+      <c r="AA4" s="50"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="51"/>
+      <c r="AE4" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="52"/>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="52"/>
-      <c r="AK4" s="52"/>
-      <c r="AL4" s="50"/>
-      <c r="AM4" s="53" t="s">
+      <c r="AF4" s="50"/>
+      <c r="AG4" s="50"/>
+      <c r="AH4" s="50"/>
+      <c r="AI4" s="50"/>
+      <c r="AJ4" s="50"/>
+      <c r="AK4" s="50"/>
+      <c r="AL4" s="51"/>
+      <c r="AM4" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="AN4" s="52"/>
-      <c r="AO4" s="52"/>
-      <c r="AP4" s="52"/>
-      <c r="AQ4" s="52"/>
-      <c r="AR4" s="52"/>
-      <c r="AS4" s="52"/>
-      <c r="AT4" s="50"/>
-      <c r="AU4" s="53" t="s">
+      <c r="AN4" s="50"/>
+      <c r="AO4" s="50"/>
+      <c r="AP4" s="50"/>
+      <c r="AQ4" s="50"/>
+      <c r="AR4" s="50"/>
+      <c r="AS4" s="50"/>
+      <c r="AT4" s="51"/>
+      <c r="AU4" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="AV4" s="52"/>
-      <c r="AW4" s="52"/>
-      <c r="AX4" s="52"/>
-      <c r="AY4" s="52"/>
-      <c r="AZ4" s="52"/>
-      <c r="BA4" s="52"/>
-      <c r="BB4" s="50"/>
-      <c r="BC4" s="54" t="s">
+      <c r="AV4" s="50"/>
+      <c r="AW4" s="50"/>
+      <c r="AX4" s="50"/>
+      <c r="AY4" s="50"/>
+      <c r="AZ4" s="50"/>
+      <c r="BA4" s="50"/>
+      <c r="BB4" s="51"/>
+      <c r="BC4" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="BD4" s="52"/>
-      <c r="BE4" s="52"/>
-      <c r="BF4" s="52"/>
-      <c r="BG4" s="52"/>
-      <c r="BH4" s="52"/>
-      <c r="BI4" s="52"/>
-      <c r="BJ4" s="50"/>
-      <c r="BK4" s="54" t="s">
+      <c r="BD4" s="50"/>
+      <c r="BE4" s="50"/>
+      <c r="BF4" s="50"/>
+      <c r="BG4" s="50"/>
+      <c r="BH4" s="50"/>
+      <c r="BI4" s="50"/>
+      <c r="BJ4" s="51"/>
+      <c r="BK4" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="BL4" s="52"/>
-      <c r="BM4" s="52"/>
-      <c r="BN4" s="52"/>
-      <c r="BO4" s="52"/>
-      <c r="BP4" s="52"/>
-      <c r="BQ4" s="52"/>
-      <c r="BR4" s="50"/>
-      <c r="BS4" s="54" t="s">
+      <c r="BL4" s="50"/>
+      <c r="BM4" s="50"/>
+      <c r="BN4" s="50"/>
+      <c r="BO4" s="50"/>
+      <c r="BP4" s="50"/>
+      <c r="BQ4" s="50"/>
+      <c r="BR4" s="51"/>
+      <c r="BS4" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="BT4" s="52"/>
-      <c r="BU4" s="52"/>
-      <c r="BV4" s="52"/>
-      <c r="BW4" s="52"/>
-      <c r="BX4" s="52"/>
-      <c r="BY4" s="52"/>
-      <c r="BZ4" s="50"/>
+      <c r="BT4" s="50"/>
+      <c r="BU4" s="50"/>
+      <c r="BV4" s="50"/>
+      <c r="BW4" s="50"/>
+      <c r="BX4" s="50"/>
+      <c r="BY4" s="50"/>
+      <c r="BZ4" s="51"/>
       <c r="CA4" s="33" t="s">
         <v>105</v>
       </c>
@@ -2947,13 +2947,13 @@
       <c r="F6" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="56" t="s">
+      <c r="G6" s="48" t="s">
         <v>139</v>
       </c>
       <c r="H6" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="I6" s="56" t="s">
+      <c r="I6" s="48" t="s">
         <v>141</v>
       </c>
       <c r="J6" s="40" t="s">
@@ -3177,140 +3177,140 @@
       </c>
     </row>
     <row r="7" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G7" s="55"/>
+      <c r="G7" s="47"/>
     </row>
     <row r="8" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G8" s="55"/>
+      <c r="G8" s="47"/>
     </row>
     <row r="9" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G9" s="55"/>
+      <c r="G9" s="47"/>
     </row>
     <row r="10" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G10" s="55"/>
+      <c r="G10" s="47"/>
     </row>
     <row r="11" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G11" s="55"/>
+      <c r="G11" s="47"/>
     </row>
     <row r="12" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G12" s="55"/>
+      <c r="G12" s="47"/>
     </row>
     <row r="13" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G13" s="55"/>
+      <c r="G13" s="47"/>
     </row>
     <row r="14" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G14" s="55"/>
+      <c r="G14" s="47"/>
     </row>
     <row r="15" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G15" s="55"/>
+      <c r="G15" s="47"/>
     </row>
     <row r="16" spans="1:82" x14ac:dyDescent="0.15">
-      <c r="G16" s="55"/>
+      <c r="G16" s="47"/>
     </row>
     <row r="17" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G17" s="55"/>
+      <c r="G17" s="47"/>
     </row>
     <row r="18" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G18" s="55"/>
+      <c r="G18" s="47"/>
     </row>
     <row r="19" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G19" s="55"/>
+      <c r="G19" s="47"/>
     </row>
     <row r="20" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G20" s="55"/>
+      <c r="G20" s="47"/>
     </row>
     <row r="21" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G21" s="55"/>
+      <c r="G21" s="47"/>
     </row>
     <row r="22" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G22" s="55"/>
+      <c r="G22" s="47"/>
     </row>
     <row r="23" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G23" s="55"/>
+      <c r="G23" s="47"/>
     </row>
     <row r="24" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G24" s="55"/>
+      <c r="G24" s="47"/>
     </row>
     <row r="25" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G25" s="55"/>
+      <c r="G25" s="47"/>
     </row>
     <row r="26" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G26" s="55"/>
+      <c r="G26" s="47"/>
     </row>
     <row r="27" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G27" s="55"/>
+      <c r="G27" s="47"/>
     </row>
     <row r="28" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G28" s="55"/>
+      <c r="G28" s="47"/>
     </row>
     <row r="29" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G29" s="55"/>
+      <c r="G29" s="47"/>
     </row>
     <row r="30" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G30" s="55"/>
+      <c r="G30" s="47"/>
     </row>
     <row r="31" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G31" s="55"/>
+      <c r="G31" s="47"/>
     </row>
     <row r="32" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G32" s="55"/>
+      <c r="G32" s="47"/>
     </row>
     <row r="33" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G33" s="55"/>
+      <c r="G33" s="47"/>
     </row>
     <row r="34" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G34" s="55"/>
+      <c r="G34" s="47"/>
     </row>
     <row r="35" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G35" s="55"/>
+      <c r="G35" s="47"/>
     </row>
     <row r="36" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G36" s="55"/>
+      <c r="G36" s="47"/>
     </row>
     <row r="37" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G37" s="55"/>
+      <c r="G37" s="47"/>
     </row>
     <row r="38" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G38" s="55"/>
+      <c r="G38" s="47"/>
     </row>
     <row r="39" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G39" s="55"/>
+      <c r="G39" s="47"/>
     </row>
     <row r="40" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G40" s="55"/>
+      <c r="G40" s="47"/>
     </row>
     <row r="41" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G41" s="55"/>
+      <c r="G41" s="47"/>
     </row>
     <row r="42" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G42" s="55"/>
+      <c r="G42" s="47"/>
     </row>
     <row r="43" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G43" s="55"/>
+      <c r="G43" s="47"/>
     </row>
     <row r="44" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G44" s="55"/>
+      <c r="G44" s="47"/>
     </row>
     <row r="45" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G45" s="55"/>
+      <c r="G45" s="47"/>
     </row>
     <row r="46" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G46" s="55"/>
+      <c r="G46" s="47"/>
     </row>
     <row r="47" spans="7:7" x14ac:dyDescent="0.15">
-      <c r="G47" s="55"/>
+      <c r="G47" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="AE4:AL4"/>
     <mergeCell ref="AM4:AT4"/>
     <mergeCell ref="AU4:BB4"/>
     <mergeCell ref="BC4:BJ4"/>
     <mergeCell ref="BK4:BR4"/>
     <mergeCell ref="BS4:BZ4"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="AE4:AL4"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="G3:H3">

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB232DE-7D8A-4F2F-843B-3A342800504F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F5D6DD-AB3A-4847-BF9A-53AEE0C6F32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8928" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1162,7 +1162,7 @@
     <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1609,14 +1609,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1624,8 +1616,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2067,42 +2067,42 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CD47"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="4.875" customWidth="1"/>
-    <col min="2" max="4" width="5.625" customWidth="1"/>
+    <col min="1" max="1" width="4.8984375" customWidth="1"/>
+    <col min="2" max="4" width="5.59765625" customWidth="1"/>
     <col min="5" max="5" width="6.5" customWidth="1"/>
-    <col min="6" max="6" width="9.625" customWidth="1"/>
+    <col min="6" max="6" width="9.59765625" customWidth="1"/>
     <col min="7" max="7" width="37.5" customWidth="1"/>
-    <col min="8" max="8" width="14.625" customWidth="1"/>
-    <col min="9" max="9" width="32.25" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="12" width="5.625" customWidth="1"/>
-    <col min="13" max="13" width="6.125" customWidth="1"/>
-    <col min="14" max="14" width="5.625" customWidth="1"/>
-    <col min="15" max="15" width="3.125" customWidth="1"/>
-    <col min="16" max="22" width="5.125" customWidth="1"/>
-    <col min="23" max="23" width="3.125" customWidth="1"/>
-    <col min="24" max="30" width="5.125" customWidth="1"/>
-    <col min="31" max="31" width="3.125" customWidth="1"/>
-    <col min="32" max="38" width="5.125" customWidth="1"/>
-    <col min="39" max="39" width="3.125" customWidth="1"/>
-    <col min="40" max="46" width="5.125" customWidth="1"/>
-    <col min="47" max="47" width="3.125" customWidth="1"/>
-    <col min="48" max="54" width="5.125" customWidth="1"/>
-    <col min="55" max="55" width="3.125" customWidth="1"/>
-    <col min="56" max="62" width="5.125" customWidth="1"/>
-    <col min="63" max="63" width="3.125" customWidth="1"/>
-    <col min="64" max="70" width="5.125" customWidth="1"/>
-    <col min="71" max="71" width="3.125" customWidth="1"/>
-    <col min="72" max="78" width="5.125" customWidth="1"/>
-    <col min="79" max="79" width="9.625" customWidth="1"/>
-    <col min="80" max="80" width="7.625" customWidth="1"/>
-    <col min="81" max="81" width="9.625" customWidth="1"/>
-    <col min="82" max="82" width="37.625" style="18" customWidth="1"/>
+    <col min="8" max="8" width="14.59765625" customWidth="1"/>
+    <col min="9" max="9" width="32.19921875" customWidth="1"/>
+    <col min="10" max="10" width="17.09765625" customWidth="1"/>
+    <col min="11" max="12" width="5.59765625" customWidth="1"/>
+    <col min="13" max="13" width="6.09765625" customWidth="1"/>
+    <col min="14" max="14" width="5.59765625" customWidth="1"/>
+    <col min="15" max="15" width="3.09765625" customWidth="1"/>
+    <col min="16" max="22" width="5.09765625" customWidth="1"/>
+    <col min="23" max="23" width="3.09765625" customWidth="1"/>
+    <col min="24" max="30" width="5.09765625" customWidth="1"/>
+    <col min="31" max="31" width="3.09765625" customWidth="1"/>
+    <col min="32" max="38" width="5.09765625" customWidth="1"/>
+    <col min="39" max="39" width="3.09765625" customWidth="1"/>
+    <col min="40" max="46" width="5.09765625" customWidth="1"/>
+    <col min="47" max="47" width="3.09765625" customWidth="1"/>
+    <col min="48" max="54" width="5.09765625" customWidth="1"/>
+    <col min="55" max="55" width="3.09765625" customWidth="1"/>
+    <col min="56" max="62" width="5.09765625" customWidth="1"/>
+    <col min="63" max="63" width="3.09765625" customWidth="1"/>
+    <col min="64" max="70" width="5.09765625" customWidth="1"/>
+    <col min="71" max="71" width="3.09765625" customWidth="1"/>
+    <col min="72" max="78" width="5.09765625" customWidth="1"/>
+    <col min="79" max="79" width="9.59765625" customWidth="1"/>
+    <col min="80" max="80" width="7.59765625" customWidth="1"/>
+    <col min="81" max="81" width="9.59765625" customWidth="1"/>
+    <col min="82" max="82" width="37.59765625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" hidden="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:82" hidden="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2350,17 +2350,17 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:82" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:82" ht="37.5" customHeight="1">
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
       <c r="J2" s="17"/>
       <c r="K2" s="20" t="s">
         <v>83</v>
@@ -2437,7 +2437,7 @@
       <c r="CC2" s="21"/>
       <c r="CD2" s="22"/>
     </row>
-    <row r="3" spans="1:82" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:82" ht="16.95" customHeight="1">
       <c r="B3" s="23">
         <f>SUM(B6:B108139)</f>
         <v>0</v>
@@ -2552,11 +2552,11 @@
       <c r="CC3" s="24"/>
       <c r="CD3" s="31"/>
     </row>
-    <row r="4" spans="1:82" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="55" t="s">
+    <row r="4" spans="1:82" ht="36" customHeight="1">
+      <c r="B4" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="51"/>
+      <c r="C4" s="52"/>
       <c r="D4" s="33" t="s">
         <v>86</v>
       </c>
@@ -2590,86 +2590,86 @@
       <c r="N4" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="56" t="s">
+      <c r="O4" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="51"/>
-      <c r="W4" s="56" t="s">
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="54"/>
+      <c r="T4" s="54"/>
+      <c r="U4" s="54"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
-      <c r="AB4" s="50"/>
-      <c r="AC4" s="50"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="49" t="s">
+      <c r="X4" s="54"/>
+      <c r="Y4" s="54"/>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="54"/>
+      <c r="AB4" s="54"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="52"/>
+      <c r="AE4" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="AF4" s="50"/>
-      <c r="AG4" s="50"/>
-      <c r="AH4" s="50"/>
-      <c r="AI4" s="50"/>
-      <c r="AJ4" s="50"/>
-      <c r="AK4" s="50"/>
-      <c r="AL4" s="51"/>
-      <c r="AM4" s="49" t="s">
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="54"/>
+      <c r="AH4" s="54"/>
+      <c r="AI4" s="54"/>
+      <c r="AJ4" s="54"/>
+      <c r="AK4" s="54"/>
+      <c r="AL4" s="52"/>
+      <c r="AM4" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="AN4" s="50"/>
-      <c r="AO4" s="50"/>
-      <c r="AP4" s="50"/>
-      <c r="AQ4" s="50"/>
-      <c r="AR4" s="50"/>
-      <c r="AS4" s="50"/>
-      <c r="AT4" s="51"/>
-      <c r="AU4" s="49" t="s">
+      <c r="AN4" s="54"/>
+      <c r="AO4" s="54"/>
+      <c r="AP4" s="54"/>
+      <c r="AQ4" s="54"/>
+      <c r="AR4" s="54"/>
+      <c r="AS4" s="54"/>
+      <c r="AT4" s="52"/>
+      <c r="AU4" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="AV4" s="50"/>
-      <c r="AW4" s="50"/>
-      <c r="AX4" s="50"/>
-      <c r="AY4" s="50"/>
-      <c r="AZ4" s="50"/>
-      <c r="BA4" s="50"/>
-      <c r="BB4" s="51"/>
-      <c r="BC4" s="52" t="s">
+      <c r="AV4" s="54"/>
+      <c r="AW4" s="54"/>
+      <c r="AX4" s="54"/>
+      <c r="AY4" s="54"/>
+      <c r="AZ4" s="54"/>
+      <c r="BA4" s="54"/>
+      <c r="BB4" s="52"/>
+      <c r="BC4" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="BD4" s="50"/>
-      <c r="BE4" s="50"/>
-      <c r="BF4" s="50"/>
-      <c r="BG4" s="50"/>
-      <c r="BH4" s="50"/>
-      <c r="BI4" s="50"/>
-      <c r="BJ4" s="51"/>
-      <c r="BK4" s="52" t="s">
+      <c r="BD4" s="54"/>
+      <c r="BE4" s="54"/>
+      <c r="BF4" s="54"/>
+      <c r="BG4" s="54"/>
+      <c r="BH4" s="54"/>
+      <c r="BI4" s="54"/>
+      <c r="BJ4" s="52"/>
+      <c r="BK4" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="BL4" s="50"/>
-      <c r="BM4" s="50"/>
-      <c r="BN4" s="50"/>
-      <c r="BO4" s="50"/>
-      <c r="BP4" s="50"/>
-      <c r="BQ4" s="50"/>
-      <c r="BR4" s="51"/>
-      <c r="BS4" s="52" t="s">
+      <c r="BL4" s="54"/>
+      <c r="BM4" s="54"/>
+      <c r="BN4" s="54"/>
+      <c r="BO4" s="54"/>
+      <c r="BP4" s="54"/>
+      <c r="BQ4" s="54"/>
+      <c r="BR4" s="52"/>
+      <c r="BS4" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="BT4" s="50"/>
-      <c r="BU4" s="50"/>
-      <c r="BV4" s="50"/>
-      <c r="BW4" s="50"/>
-      <c r="BX4" s="50"/>
-      <c r="BY4" s="50"/>
-      <c r="BZ4" s="51"/>
+      <c r="BT4" s="54"/>
+      <c r="BU4" s="54"/>
+      <c r="BV4" s="54"/>
+      <c r="BW4" s="54"/>
+      <c r="BX4" s="54"/>
+      <c r="BY4" s="54"/>
+      <c r="BZ4" s="52"/>
       <c r="CA4" s="33" t="s">
         <v>105</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:82" ht="48" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:82" ht="48" customHeight="1">
       <c r="B5" s="32" t="s">
         <v>109</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:82" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:82" s="17" customFormat="1" ht="57">
       <c r="A6" s="38" t="s">
         <v>133</v>
       </c>
@@ -3176,141 +3176,141 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:82">
       <c r="G7" s="47"/>
     </row>
-    <row r="8" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:82">
       <c r="G8" s="47"/>
     </row>
-    <row r="9" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:82">
       <c r="G9" s="47"/>
     </row>
-    <row r="10" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:82">
       <c r="G10" s="47"/>
     </row>
-    <row r="11" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:82">
       <c r="G11" s="47"/>
     </row>
-    <row r="12" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:82">
       <c r="G12" s="47"/>
     </row>
-    <row r="13" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:82">
       <c r="G13" s="47"/>
     </row>
-    <row r="14" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:82">
       <c r="G14" s="47"/>
     </row>
-    <row r="15" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:82">
       <c r="G15" s="47"/>
     </row>
-    <row r="16" spans="1:82" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:82">
       <c r="G16" s="47"/>
     </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="7:7">
       <c r="G17" s="47"/>
     </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="18" spans="7:7">
       <c r="G18" s="47"/>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="7:7">
       <c r="G19" s="47"/>
     </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="7:7">
       <c r="G20" s="47"/>
     </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="21" spans="7:7">
       <c r="G21" s="47"/>
     </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="7:7">
       <c r="G22" s="47"/>
     </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="7:7">
       <c r="G23" s="47"/>
     </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="7:7">
       <c r="G24" s="47"/>
     </row>
-    <row r="25" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="7:7">
       <c r="G25" s="47"/>
     </row>
-    <row r="26" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="26" spans="7:7">
       <c r="G26" s="47"/>
     </row>
-    <row r="27" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="7:7">
       <c r="G27" s="47"/>
     </row>
-    <row r="28" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="28" spans="7:7">
       <c r="G28" s="47"/>
     </row>
-    <row r="29" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="7:7">
       <c r="G29" s="47"/>
     </row>
-    <row r="30" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="7:7">
       <c r="G30" s="47"/>
     </row>
-    <row r="31" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="7:7">
       <c r="G31" s="47"/>
     </row>
-    <row r="32" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="7:7">
       <c r="G32" s="47"/>
     </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="7:7">
       <c r="G33" s="47"/>
     </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="7:7">
       <c r="G34" s="47"/>
     </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="35" spans="7:7">
       <c r="G35" s="47"/>
     </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="36" spans="7:7">
       <c r="G36" s="47"/>
     </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="37" spans="7:7">
       <c r="G37" s="47"/>
     </row>
-    <row r="38" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="38" spans="7:7">
       <c r="G38" s="47"/>
     </row>
-    <row r="39" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="7:7">
       <c r="G39" s="47"/>
     </row>
-    <row r="40" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="7:7">
       <c r="G40" s="47"/>
     </row>
-    <row r="41" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="7:7">
       <c r="G41" s="47"/>
     </row>
-    <row r="42" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="42" spans="7:7">
       <c r="G42" s="47"/>
     </row>
-    <row r="43" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="43" spans="7:7">
       <c r="G43" s="47"/>
     </row>
-    <row r="44" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="7:7">
       <c r="G44" s="47"/>
     </row>
-    <row r="45" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="7:7">
       <c r="G45" s="47"/>
     </row>
-    <row r="46" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="46" spans="7:7">
       <c r="G46" s="47"/>
     </row>
-    <row r="47" spans="7:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="7:7">
       <c r="G47" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AM4:AT4"/>
+    <mergeCell ref="AU4:BB4"/>
+    <mergeCell ref="BC4:BJ4"/>
+    <mergeCell ref="BK4:BR4"/>
+    <mergeCell ref="BS4:BZ4"/>
     <mergeCell ref="E2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="O4:V4"/>
     <mergeCell ref="W4:AD4"/>
     <mergeCell ref="AE4:AL4"/>
-    <mergeCell ref="AM4:AT4"/>
-    <mergeCell ref="AU4:BB4"/>
-    <mergeCell ref="BC4:BJ4"/>
-    <mergeCell ref="BK4:BR4"/>
-    <mergeCell ref="BS4:BZ4"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="G3:H3">
@@ -3333,25 +3333,25 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
   <cols>
     <col min="1" max="1" width="4.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="3" customWidth="1"/>
-    <col min="3" max="4" width="5.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="5.25" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="34.125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="34.125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="5" customWidth="1"/>
-    <col min="11" max="11" width="6.75" style="5" customWidth="1"/>
-    <col min="12" max="14" width="6.75" style="4" customWidth="1"/>
-    <col min="15" max="16" width="27.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.8984375" style="3" customWidth="1"/>
+    <col min="3" max="4" width="5.59765625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="5.19921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.19921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.09765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="34.09765625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.69921875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="25.5" style="5" customWidth="1"/>
+    <col min="12" max="14" width="6.69921875" style="4" customWidth="1"/>
+    <col min="15" max="16" width="27.3984375" style="4" customWidth="1"/>
     <col min="17" max="17" width="8" style="4" customWidth="1"/>
     <col min="18" max="16384" width="8" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" hidden="1">
       <c r="A1" s="2" t="s">
         <v>215</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" ht="33.75" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -3421,7 +3421,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16" s="1" customFormat="1" ht="34.200000000000003" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>232</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" s="1" customFormat="1" ht="68.25" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>245</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="11.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" ht="11.4" customHeight="1">
       <c r="A5" s="13" t="s">
         <v>259</v>
       </c>
